--- a/documentacion/DD Proyecto.xlsx
+++ b/documentacion/DD Proyecto.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shavi\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shavi\Downloads\visual\Proyecto\RBE\documentacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F066540-CC27-4FA6-87DF-808ACB6DB80F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCCBB231-232C-45B0-B2F2-6A240FB6C2FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DICCIONARIO DE DATOS" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="113">
   <si>
     <t>Número</t>
   </si>
@@ -362,6 +362,9 @@
   </si>
   <si>
     <t>Registrar a los empleados encargados de ventas en terminales.</t>
+  </si>
+  <si>
+    <t>FechaHora</t>
   </si>
 </sst>
 </file>
@@ -452,18 +455,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -472,22 +475,19 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -808,15 +808,15 @@
   </cols>
   <sheetData>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="11" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="12" t="s">
         <v>93</v>
       </c>
       <c r="B5" t="s">
@@ -869,7 +869,7 @@
       <c r="C8" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="D8" s="10">
+      <c r="D8" s="7">
         <v>30</v>
       </c>
       <c r="E8" s="8" t="s">
@@ -944,15 +944,15 @@
       <c r="F12" s="9"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="13" t="s">
+      <c r="A14" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="11" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="13" t="s">
+      <c r="A15" s="12" t="s">
         <v>93</v>
       </c>
       <c r="B15" s="1" t="s">
@@ -1005,7 +1005,7 @@
       <c r="C18" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="D18" s="10">
+      <c r="D18" s="7">
         <v>30</v>
       </c>
       <c r="E18" s="8" t="s">
@@ -1023,7 +1023,7 @@
       <c r="C19" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="D19" s="10">
+      <c r="D19" s="7">
         <v>30</v>
       </c>
       <c r="E19" s="8" t="s">
@@ -1041,7 +1041,7 @@
       <c r="C20" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="D20" s="10">
+      <c r="D20" s="7">
         <v>30</v>
       </c>
       <c r="E20" s="8"/>
@@ -1057,7 +1057,7 @@
       <c r="C21" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="D21" s="10">
+      <c r="D21" s="7">
         <v>15</v>
       </c>
       <c r="E21" s="8" t="s">
@@ -1072,7 +1072,7 @@
       <c r="B22" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C22" s="11" t="s">
+      <c r="C22" s="10" t="s">
         <v>69</v>
       </c>
       <c r="D22" s="7"/>
@@ -1088,7 +1088,7 @@
       <c r="B23" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C23" s="11" t="s">
+      <c r="C23" s="10" t="s">
         <v>69</v>
       </c>
       <c r="D23" s="7"/>
@@ -1098,7 +1098,7 @@
       <c r="F23" s="9"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="13" t="s">
+      <c r="A25" s="12" t="s">
         <v>75</v>
       </c>
       <c r="B25" s="1" t="s">
@@ -1106,7 +1106,7 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="13" t="s">
+      <c r="A26" s="12" t="s">
         <v>93</v>
       </c>
       <c r="B26" s="1" t="s">
@@ -1143,7 +1143,7 @@
       <c r="C28" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="D28" s="10">
+      <c r="D28" s="7">
         <v>5</v>
       </c>
       <c r="E28" s="8" t="s">
@@ -1161,7 +1161,7 @@
       <c r="C29" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="D29" s="10">
+      <c r="D29" s="7">
         <v>30</v>
       </c>
       <c r="E29" s="8" t="s">
@@ -1170,7 +1170,7 @@
       <c r="F29" s="9"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="13" t="s">
+      <c r="A31" s="12" t="s">
         <v>75</v>
       </c>
       <c r="B31" s="1" t="s">
@@ -1178,7 +1178,7 @@
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="13" t="s">
+      <c r="A32" s="12" t="s">
         <v>93</v>
       </c>
       <c r="B32" s="1" t="s">
@@ -1215,7 +1215,7 @@
       <c r="C34" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="D34" s="10">
+      <c r="D34" s="7">
         <v>5</v>
       </c>
       <c r="E34" s="8" t="s">
@@ -1233,7 +1233,7 @@
       <c r="C35" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="D35" s="10">
+      <c r="D35" s="7">
         <v>30</v>
       </c>
       <c r="E35" s="8" t="s">
@@ -1242,7 +1242,7 @@
       <c r="F35" s="9"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="13" t="s">
+      <c r="A37" s="12" t="s">
         <v>75</v>
       </c>
       <c r="B37" s="1" t="s">
@@ -1250,7 +1250,7 @@
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="13" t="s">
+      <c r="A38" s="12" t="s">
         <v>93</v>
       </c>
       <c r="B38" s="1" t="s">
@@ -1317,7 +1317,7 @@
       <c r="C42" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="D42" s="10">
+      <c r="D42" s="7">
         <v>30</v>
       </c>
       <c r="E42" s="8" t="s">
@@ -1326,7 +1326,7 @@
       <c r="F42" s="9"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="13" t="s">
+      <c r="A44" s="12" t="s">
         <v>75</v>
       </c>
       <c r="B44" s="1" t="s">
@@ -1334,7 +1334,7 @@
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="13" t="s">
+      <c r="A45" s="12" t="s">
         <v>93</v>
       </c>
       <c r="B45" s="1" t="s">
@@ -1384,10 +1384,10 @@
       <c r="B48" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C48" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="D48" s="10">
+      <c r="C48" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="D48" s="7">
         <v>30</v>
       </c>
       <c r="E48" s="8" t="s">
@@ -1402,10 +1402,10 @@
       <c r="B49" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C49" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="D49" s="10">
+      <c r="C49" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="D49" s="7">
         <v>50</v>
       </c>
       <c r="E49" s="8" t="s">
@@ -1414,7 +1414,7 @@
       <c r="F49" s="9"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="13" t="s">
+      <c r="A51" s="12" t="s">
         <v>75</v>
       </c>
       <c r="B51" s="1" t="s">
@@ -1422,7 +1422,7 @@
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="13" t="s">
+      <c r="A52" s="12" t="s">
         <v>93</v>
       </c>
       <c r="B52" s="1" t="s">
@@ -1475,7 +1475,7 @@
       <c r="C55" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="D55" s="10">
+      <c r="D55" s="7">
         <v>30</v>
       </c>
       <c r="E55" s="8" t="s">
@@ -1493,7 +1493,7 @@
       <c r="C56" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="D56" s="10">
+      <c r="D56" s="7">
         <v>50</v>
       </c>
       <c r="E56" s="8" t="s">
@@ -1502,7 +1502,7 @@
       <c r="F56" s="9"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="13" t="s">
+      <c r="A58" s="12" t="s">
         <v>75</v>
       </c>
       <c r="B58" s="1" t="s">
@@ -1510,7 +1510,7 @@
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="13" t="s">
+      <c r="A59" s="12" t="s">
         <v>93</v>
       </c>
       <c r="B59" s="1" t="s">
@@ -1563,7 +1563,7 @@
       <c r="C62" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="D62" s="10">
+      <c r="D62" s="7">
         <v>30</v>
       </c>
       <c r="E62" s="8" t="s">
@@ -1581,7 +1581,7 @@
       <c r="C63" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="D63" s="10">
+      <c r="D63" s="7">
         <v>30</v>
       </c>
       <c r="E63" s="8" t="s">
@@ -1599,7 +1599,7 @@
       <c r="C64" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="D64" s="10">
+      <c r="D64" s="7">
         <v>10</v>
       </c>
       <c r="E64" s="8" t="s">
@@ -1617,7 +1617,7 @@
       <c r="C65" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="D65" s="10">
+      <c r="D65" s="7">
         <v>30</v>
       </c>
       <c r="E65" s="8" t="s">
@@ -1635,7 +1635,7 @@
       <c r="C66" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="D66" s="10">
+      <c r="D66" s="7">
         <v>5</v>
       </c>
       <c r="E66" s="8" t="s">
@@ -1644,7 +1644,7 @@
       <c r="F66" s="9"/>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="13" t="s">
+      <c r="A68" s="12" t="s">
         <v>75</v>
       </c>
       <c r="B68" s="1" t="s">
@@ -1652,7 +1652,7 @@
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="13" t="s">
+      <c r="A69" s="12" t="s">
         <v>93</v>
       </c>
       <c r="B69" s="1" t="s">
@@ -1689,7 +1689,7 @@
       <c r="C71" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="D71" s="10">
+      <c r="D71" s="7">
         <v>5</v>
       </c>
       <c r="E71" s="8" t="s">
@@ -1697,19 +1697,21 @@
       </c>
       <c r="F71" s="9"/>
     </row>
-    <row r="72" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" s="7">
         <v>2</v>
       </c>
       <c r="B72" s="7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="D72" s="7"/>
+        <v>68</v>
+      </c>
+      <c r="D72" s="7">
+        <v>10</v>
+      </c>
       <c r="E72" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F72" s="9"/>
     </row>
@@ -1718,7 +1720,7 @@
         <v>3</v>
       </c>
       <c r="B73" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C73" s="7" t="s">
         <v>66</v>
@@ -1729,26 +1731,24 @@
       </c>
       <c r="F73" s="9"/>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A74" s="7">
         <v>4</v>
       </c>
       <c r="B74" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="D74" s="10">
-        <v>10</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="D74" s="7"/>
       <c r="E74" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F74" s="9"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" s="13" t="s">
+      <c r="A76" s="12" t="s">
         <v>75</v>
       </c>
       <c r="B76" s="1" t="s">
@@ -1756,7 +1756,7 @@
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A77" s="13" t="s">
+      <c r="A77" s="12" t="s">
         <v>93</v>
       </c>
       <c r="B77" s="1" t="s">
@@ -1806,7 +1806,7 @@
       <c r="B80" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C80" s="11" t="s">
+      <c r="C80" s="10" t="s">
         <v>69</v>
       </c>
       <c r="D80" s="7"/>
@@ -1857,7 +1857,7 @@
       <c r="C83" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="D83" s="10">
+      <c r="D83" s="7">
         <v>5</v>
       </c>
       <c r="E83" s="8" t="s">
@@ -1882,7 +1882,7 @@
       <c r="F84" s="9"/>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86" s="13" t="s">
+      <c r="A86" s="12" t="s">
         <v>75</v>
       </c>
       <c r="B86" s="1" t="s">
@@ -1890,7 +1890,7 @@
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87" s="13" t="s">
+      <c r="A87" s="12" t="s">
         <v>93</v>
       </c>
       <c r="B87" s="1" t="s">
@@ -1959,7 +1959,7 @@
       <c r="C91" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="D91" s="10">
+      <c r="D91" s="7">
         <v>10</v>
       </c>
       <c r="E91" s="8" t="s">
@@ -1968,7 +1968,7 @@
       <c r="F91" s="9"/>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A93" s="13" t="s">
+      <c r="A93" s="12" t="s">
         <v>75</v>
       </c>
       <c r="B93" s="1" t="s">
@@ -1976,7 +1976,7 @@
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A94" s="13" t="s">
+      <c r="A94" s="12" t="s">
         <v>93</v>
       </c>
       <c r="B94" s="1" t="s">
@@ -2052,7 +2052,7 @@
       <c r="F98" s="9"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A100" s="13" t="s">
+      <c r="A100" s="12" t="s">
         <v>75</v>
       </c>
       <c r="B100" s="1" t="s">
@@ -2060,7 +2060,7 @@
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A101" s="13" t="s">
+      <c r="A101" s="12" t="s">
         <v>93</v>
       </c>
       <c r="B101" s="1" t="s">
@@ -2126,10 +2126,10 @@
       <c r="B105" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="C105" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="D105" s="10">
+      <c r="C105" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="D105" s="7">
         <v>5</v>
       </c>
       <c r="E105" s="8" t="s">
@@ -2154,7 +2154,7 @@
       <c r="F106" s="9"/>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A108" s="13" t="s">
+      <c r="A108" s="12" t="s">
         <v>75</v>
       </c>
       <c r="B108" s="1" t="s">
@@ -2162,7 +2162,7 @@
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A109" s="13" t="s">
+      <c r="A109" s="12" t="s">
         <v>93</v>
       </c>
       <c r="B109" s="1" t="s">
@@ -2215,7 +2215,7 @@
       <c r="C112" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="D112" s="10">
+      <c r="D112" s="7">
         <v>30</v>
       </c>
       <c r="E112" s="8" t="s">
@@ -2233,7 +2233,7 @@
       <c r="C113" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="D113" s="10">
+      <c r="D113" s="7">
         <v>30</v>
       </c>
       <c r="E113" s="8" t="s">
@@ -2251,7 +2251,7 @@
       <c r="C114" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="D114" s="10">
+      <c r="D114" s="7">
         <v>30</v>
       </c>
       <c r="E114" s="8"/>
@@ -2288,7 +2288,7 @@
       <c r="F116" s="9"/>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A118" s="13" t="s">
+      <c r="A118" s="12" t="s">
         <v>75</v>
       </c>
       <c r="B118" s="1" t="s">
@@ -2296,7 +2296,7 @@
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A119" s="13" t="s">
+      <c r="A119" s="12" t="s">
         <v>93</v>
       </c>
       <c r="B119" s="1" t="s">
@@ -2333,7 +2333,7 @@
       <c r="C121" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="D121" s="10">
+      <c r="D121" s="7">
         <v>10</v>
       </c>
       <c r="E121" s="8" t="s">
@@ -2365,7 +2365,7 @@
         <v>52</v>
       </c>
       <c r="C123" s="7" t="s">
-        <v>69</v>
+        <v>112</v>
       </c>
       <c r="D123" s="7"/>
       <c r="E123" s="8" t="s">
@@ -2447,7 +2447,7 @@
       <c r="C128" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="D128" s="10">
+      <c r="D128" s="7">
         <v>5</v>
       </c>
       <c r="E128" s="8" t="s">
@@ -2472,7 +2472,7 @@
       <c r="F129" s="9"/>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A131" s="13" t="s">
+      <c r="A131" s="12" t="s">
         <v>75</v>
       </c>
       <c r="B131" s="1" t="s">
@@ -2480,7 +2480,7 @@
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A132" s="13" t="s">
+      <c r="A132" s="12" t="s">
         <v>93</v>
       </c>
       <c r="B132" s="1" t="s">
@@ -2517,7 +2517,7 @@
       <c r="C134" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="D134" s="10">
+      <c r="D134" s="7">
         <v>5</v>
       </c>
       <c r="E134" s="8" t="s">
@@ -2533,7 +2533,7 @@
         <v>58</v>
       </c>
       <c r="C135" s="7" t="s">
-        <v>69</v>
+        <v>112</v>
       </c>
       <c r="D135" s="7"/>
       <c r="E135" s="8" t="s">
@@ -2574,7 +2574,7 @@
       <c r="F137" s="9"/>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A139" s="13" t="s">
+      <c r="A139" s="12" t="s">
         <v>75</v>
       </c>
       <c r="B139" s="1" t="s">
@@ -2582,7 +2582,7 @@
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A140" s="13" t="s">
+      <c r="A140" s="12" t="s">
         <v>93</v>
       </c>
       <c r="B140" s="1" t="s">
@@ -2635,7 +2635,7 @@
       <c r="C143" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="D143" s="10">
+      <c r="D143" s="7">
         <v>30</v>
       </c>
       <c r="E143" s="8" t="s">
@@ -2653,7 +2653,7 @@
       <c r="C144" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="D144" s="10">
+      <c r="D144" s="7">
         <v>30</v>
       </c>
       <c r="E144" s="8" t="s">
@@ -2671,7 +2671,7 @@
       <c r="C145" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="D145" s="10">
+      <c r="D145" s="7">
         <v>30</v>
       </c>
       <c r="E145" s="8"/>
@@ -2703,7 +2703,7 @@
       <c r="C147" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="D147" s="10">
+      <c r="D147" s="7">
         <v>20</v>
       </c>
       <c r="E147" s="8" t="s">
@@ -2721,7 +2721,7 @@
       <c r="C148" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="D148" s="10">
+      <c r="D148" s="7">
         <v>20</v>
       </c>
       <c r="E148" s="8" t="s">

--- a/documentacion/DD Proyecto.xlsx
+++ b/documentacion/DD Proyecto.xlsx
@@ -73,7 +73,7 @@
     <t>anio</t>
   </si>
   <si>
-    <t>capacidad</t>
+    <t>cre</t>
   </si>
   <si>
     <t>marca</t>

--- a/documentacion/DD Proyecto.xlsx
+++ b/documentacion/DD Proyecto.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\52664\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shavi\Downloads\visual\Proyecto\RBE\documentacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C467BFB1-A06E-4110-A3DD-D5BCE986FB8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E46209B4-BF96-48FD-8E7E-59C9A9130545}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15360" yWindow="0" windowWidth="7776" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DICCIONARIO DE DATOS" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="140">
   <si>
     <t>Número</t>
   </si>
@@ -454,6 +454,12 @@
   </si>
   <si>
     <t>Es el numero que identifica el tipo de pago</t>
+  </si>
+  <si>
+    <t>VIAJE_ASIENTO</t>
+  </si>
+  <si>
+    <t>Asociar el estado de un asiento en un viaje especifico.</t>
   </si>
 </sst>
 </file>
@@ -884,19 +890,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A4:F149"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A4:F155"/>
+  <sheetFormatPr defaultColWidth="11.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.08984375" style="2"/>
-    <col min="2" max="2" width="16.6328125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="13.36328125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="11.08984375" style="2"/>
-    <col min="5" max="5" width="11.08984375" style="3"/>
-    <col min="6" max="6" width="33.36328125" style="4" customWidth="1"/>
-    <col min="7" max="16384" width="11.08984375" style="2"/>
+    <col min="1" max="1" width="11.109375" style="2"/>
+    <col min="2" max="2" width="16.6640625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="11.109375" style="2"/>
+    <col min="5" max="5" width="11.109375" style="3"/>
+    <col min="6" max="6" width="33.33203125" style="4" customWidth="1"/>
+    <col min="7" max="16384" width="11.109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="12" t="s">
         <v>75</v>
       </c>
@@ -904,7 +910,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="12" t="s">
         <v>93</v>
       </c>
@@ -912,7 +918,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>0</v>
       </c>
@@ -932,7 +938,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="7">
         <v>1</v>
       </c>
@@ -950,7 +956,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="7">
         <v>2</v>
       </c>
@@ -970,7 +976,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="7">
         <v>3</v>
       </c>
@@ -988,7 +994,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="7">
         <v>4</v>
       </c>
@@ -1006,7 +1012,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="7">
         <v>5</v>
       </c>
@@ -1024,7 +1030,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="7">
         <v>6</v>
       </c>
@@ -1044,7 +1050,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
         <v>75</v>
       </c>
@@ -1052,7 +1058,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="12" t="s">
         <v>93</v>
       </c>
@@ -1060,7 +1066,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>0</v>
       </c>
@@ -1080,7 +1086,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="7">
         <v>1</v>
       </c>
@@ -1096,7 +1102,7 @@
       </c>
       <c r="F17" s="8"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="7">
         <v>2</v>
       </c>
@@ -1116,7 +1122,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="7">
         <v>3</v>
       </c>
@@ -1136,7 +1142,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="7">
         <v>4</v>
       </c>
@@ -1154,7 +1160,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="7">
         <v>5</v>
       </c>
@@ -1174,7 +1180,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A22" s="7">
         <v>6</v>
       </c>
@@ -1192,7 +1198,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A23" s="7">
         <v>7</v>
       </c>
@@ -1210,7 +1216,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="12" t="s">
         <v>75</v>
       </c>
@@ -1218,7 +1224,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="12" t="s">
         <v>93</v>
       </c>
@@ -1226,7 +1232,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>0</v>
       </c>
@@ -1246,7 +1252,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="7">
         <v>1</v>
       </c>
@@ -1266,7 +1272,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="7">
         <v>2</v>
       </c>
@@ -1286,7 +1292,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="12" t="s">
         <v>75</v>
       </c>
@@ -1294,7 +1300,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="12" t="s">
         <v>93</v>
       </c>
@@ -1302,7 +1308,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
         <v>0</v>
       </c>
@@ -1322,7 +1328,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A34" s="7">
         <v>1</v>
       </c>
@@ -1342,7 +1348,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A35" s="7">
         <v>2</v>
       </c>
@@ -1362,7 +1368,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="12" t="s">
         <v>75</v>
       </c>
@@ -1370,7 +1376,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="12" t="s">
         <v>93</v>
       </c>
@@ -1378,7 +1384,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
         <v>0</v>
       </c>
@@ -1398,7 +1404,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A40" s="7">
         <v>1</v>
       </c>
@@ -1416,7 +1422,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="7">
         <v>2</v>
       </c>
@@ -1434,7 +1440,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="42" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A42" s="7">
         <v>3</v>
       </c>
@@ -1454,7 +1460,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" s="12" t="s">
         <v>75</v>
       </c>
@@ -1462,7 +1468,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" s="12" t="s">
         <v>93</v>
       </c>
@@ -1470,7 +1476,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
         <v>0</v>
       </c>
@@ -1490,7 +1496,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A47" s="7">
         <v>1</v>
       </c>
@@ -1508,7 +1514,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" s="7">
         <v>2</v>
       </c>
@@ -1526,7 +1532,7 @@
       </c>
       <c r="F48" s="9"/>
     </row>
-    <row r="49" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A49" s="7">
         <v>3</v>
       </c>
@@ -1544,7 +1550,7 @@
       </c>
       <c r="F49" s="9"/>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" s="12" t="s">
         <v>75</v>
       </c>
@@ -1552,7 +1558,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" s="12" t="s">
         <v>93</v>
       </c>
@@ -1560,7 +1566,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" s="5" t="s">
         <v>0</v>
       </c>
@@ -1580,7 +1586,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" s="7">
         <v>1</v>
       </c>
@@ -1596,7 +1602,7 @@
       </c>
       <c r="F54" s="9"/>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" s="7">
         <v>2</v>
       </c>
@@ -1614,7 +1620,7 @@
       </c>
       <c r="F55" s="9"/>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" s="7">
         <v>3</v>
       </c>
@@ -1632,7 +1638,7 @@
       </c>
       <c r="F56" s="9"/>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" s="12" t="s">
         <v>75</v>
       </c>
@@ -1640,7 +1646,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" s="12" t="s">
         <v>93</v>
       </c>
@@ -1648,7 +1654,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" s="5" t="s">
         <v>0</v>
       </c>
@@ -1668,7 +1674,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" s="7">
         <v>1</v>
       </c>
@@ -1684,7 +1690,7 @@
       </c>
       <c r="F61" s="9"/>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" s="7">
         <v>2</v>
       </c>
@@ -1702,7 +1708,7 @@
       </c>
       <c r="F62" s="9"/>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" s="7">
         <v>3</v>
       </c>
@@ -1720,7 +1726,7 @@
       </c>
       <c r="F63" s="9"/>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" s="7">
         <v>4</v>
       </c>
@@ -1738,7 +1744,7 @@
       </c>
       <c r="F64" s="9"/>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" s="7">
         <v>5</v>
       </c>
@@ -1756,7 +1762,7 @@
       </c>
       <c r="F65" s="9"/>
     </row>
-    <row r="66" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A66" s="7">
         <v>6</v>
       </c>
@@ -1774,7 +1780,7 @@
       </c>
       <c r="F66" s="9"/>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" s="12" t="s">
         <v>75</v>
       </c>
@@ -1782,7 +1788,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" s="12" t="s">
         <v>93</v>
       </c>
@@ -1790,7 +1796,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" s="5" t="s">
         <v>0</v>
       </c>
@@ -1810,7 +1816,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A71" s="7">
         <v>1</v>
       </c>
@@ -1828,7 +1834,7 @@
       </c>
       <c r="F71" s="9"/>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" s="7">
         <v>2</v>
       </c>
@@ -1846,7 +1852,7 @@
       </c>
       <c r="F72" s="9"/>
     </row>
-    <row r="73" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A73" s="7">
         <v>3</v>
       </c>
@@ -1862,7 +1868,7 @@
       </c>
       <c r="F73" s="9"/>
     </row>
-    <row r="74" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A74" s="7">
         <v>4</v>
       </c>
@@ -1878,7 +1884,7 @@
       </c>
       <c r="F74" s="9"/>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" s="12" t="s">
         <v>75</v>
       </c>
@@ -1886,7 +1892,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" s="12" t="s">
         <v>93</v>
       </c>
@@ -1894,7 +1900,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" s="5" t="s">
         <v>0</v>
       </c>
@@ -1914,7 +1920,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="79" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A79" s="7">
         <v>1</v>
       </c>
@@ -1930,7 +1936,7 @@
       </c>
       <c r="F79" s="9"/>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" s="7">
         <v>2</v>
       </c>
@@ -1946,7 +1952,7 @@
       </c>
       <c r="F80" s="9"/>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" s="7">
         <v>3</v>
       </c>
@@ -1962,7 +1968,7 @@
       </c>
       <c r="F81" s="9"/>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" s="7">
         <v>4</v>
       </c>
@@ -1978,7 +1984,7 @@
       </c>
       <c r="F82" s="9"/>
     </row>
-    <row r="83" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A83" s="7">
         <v>5</v>
       </c>
@@ -1996,7 +2002,7 @@
       </c>
       <c r="F83" s="9"/>
     </row>
-    <row r="84" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A84" s="7">
         <v>6</v>
       </c>
@@ -2012,7 +2018,7 @@
       </c>
       <c r="F84" s="9"/>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" s="12" t="s">
         <v>75</v>
       </c>
@@ -2020,7 +2026,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" s="12" t="s">
         <v>93</v>
       </c>
@@ -2028,7 +2034,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88" s="5" t="s">
         <v>0</v>
       </c>
@@ -2048,7 +2054,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89" s="7">
         <v>1</v>
       </c>
@@ -2064,7 +2070,7 @@
       </c>
       <c r="F89" s="8"/>
     </row>
-    <row r="90" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A90" s="7">
         <v>2</v>
       </c>
@@ -2082,7 +2088,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="91" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A91" s="7">
         <v>3</v>
       </c>
@@ -2102,7 +2108,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93" s="12" t="s">
         <v>75</v>
       </c>
@@ -2110,7 +2116,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" s="12" t="s">
         <v>93</v>
       </c>
@@ -2118,7 +2124,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95" s="5" t="s">
         <v>0</v>
       </c>
@@ -2138,7 +2144,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96" s="7">
         <v>1</v>
       </c>
@@ -2154,7 +2160,7 @@
       </c>
       <c r="F96" s="9"/>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97" s="7">
         <v>2</v>
       </c>
@@ -2170,7 +2176,7 @@
       </c>
       <c r="F97" s="9"/>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98" s="7">
         <v>3</v>
       </c>
@@ -2186,7 +2192,7 @@
       </c>
       <c r="F98" s="9"/>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100" s="12" t="s">
         <v>75</v>
       </c>
@@ -2194,7 +2200,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101" s="12" t="s">
         <v>93</v>
       </c>
@@ -2202,7 +2208,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102" s="5" t="s">
         <v>0</v>
       </c>
@@ -2222,7 +2228,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="103" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A103" s="7">
         <v>1</v>
       </c>
@@ -2240,7 +2246,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="104" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A104" s="7">
         <v>2</v>
       </c>
@@ -2258,7 +2264,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="105" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A105" s="7">
         <v>3</v>
       </c>
@@ -2276,7 +2282,7 @@
       </c>
       <c r="F105" s="9"/>
     </row>
-    <row r="106" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A106" s="7">
         <v>4</v>
       </c>
@@ -2292,7 +2298,7 @@
       </c>
       <c r="F106" s="9"/>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108" s="12" t="s">
         <v>75</v>
       </c>
@@ -2300,7 +2306,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109" s="12" t="s">
         <v>93</v>
       </c>
@@ -2308,7 +2314,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A110" s="5" t="s">
         <v>0</v>
       </c>
@@ -2328,7 +2334,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="111" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A111" s="7">
         <v>1</v>
       </c>
@@ -2344,7 +2350,7 @@
       </c>
       <c r="F111" s="9"/>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A112" s="7">
         <v>2</v>
       </c>
@@ -2362,7 +2368,7 @@
       </c>
       <c r="F112" s="9"/>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A113" s="7">
         <v>3</v>
       </c>
@@ -2380,7 +2386,7 @@
       </c>
       <c r="F113" s="9"/>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A114" s="7">
         <v>4</v>
       </c>
@@ -2396,7 +2402,7 @@
       <c r="E114" s="8"/>
       <c r="F114" s="9"/>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A115" s="7">
         <v>5</v>
       </c>
@@ -2412,7 +2418,7 @@
       </c>
       <c r="F115" s="9"/>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A116" s="7">
         <v>6</v>
       </c>
@@ -2426,7 +2432,7 @@
       <c r="E116" s="8"/>
       <c r="F116" s="9"/>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A118" s="12" t="s">
         <v>75</v>
       </c>
@@ -2434,7 +2440,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A119" s="12" t="s">
         <v>93</v>
       </c>
@@ -2442,7 +2448,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A120" s="5" t="s">
         <v>0</v>
       </c>
@@ -2462,7 +2468,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="121" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A121" s="7">
         <v>1</v>
       </c>
@@ -2480,7 +2486,7 @@
       </c>
       <c r="F121" s="9"/>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A122" s="7">
         <v>2</v>
       </c>
@@ -2496,7 +2502,7 @@
       </c>
       <c r="F122" s="9"/>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A123" s="7">
         <v>3</v>
       </c>
@@ -2512,7 +2518,7 @@
       </c>
       <c r="F123" s="9"/>
     </row>
-    <row r="124" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A124" s="7">
         <v>4</v>
       </c>
@@ -2528,7 +2534,7 @@
       </c>
       <c r="F124" s="9"/>
     </row>
-    <row r="125" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A125" s="7">
         <v>5</v>
       </c>
@@ -2544,7 +2550,7 @@
       </c>
       <c r="F125" s="9"/>
     </row>
-    <row r="126" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A126" s="7">
         <v>6</v>
       </c>
@@ -2560,7 +2566,7 @@
       </c>
       <c r="F126" s="9"/>
     </row>
-    <row r="127" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A127" s="7">
         <v>7</v>
       </c>
@@ -2576,7 +2582,7 @@
       </c>
       <c r="F127" s="9"/>
     </row>
-    <row r="128" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A128" s="7">
         <v>8</v>
       </c>
@@ -2594,7 +2600,7 @@
       </c>
       <c r="F128" s="9"/>
     </row>
-    <row r="129" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A129" s="7">
         <v>9</v>
       </c>
@@ -2610,7 +2616,7 @@
       </c>
       <c r="F129" s="9"/>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A131" s="12" t="s">
         <v>75</v>
       </c>
@@ -2618,7 +2624,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A132" s="12" t="s">
         <v>93</v>
       </c>
@@ -2626,7 +2632,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A133" s="5" t="s">
         <v>0</v>
       </c>
@@ -2646,7 +2652,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="134" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A134" s="7">
         <v>1</v>
       </c>
@@ -2664,7 +2670,7 @@
       </c>
       <c r="F134" s="9"/>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A135" s="7">
         <v>2</v>
       </c>
@@ -2680,7 +2686,7 @@
       </c>
       <c r="F135" s="9"/>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A136" s="7">
         <v>3</v>
       </c>
@@ -2696,7 +2702,7 @@
       </c>
       <c r="F136" s="9"/>
     </row>
-    <row r="137" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A137" s="7">
         <v>4</v>
       </c>
@@ -2712,7 +2718,7 @@
       </c>
       <c r="F137" s="9"/>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A139" s="12" t="s">
         <v>75</v>
       </c>
@@ -2720,7 +2726,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A140" s="12" t="s">
         <v>93</v>
       </c>
@@ -2728,7 +2734,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A141" s="5" t="s">
         <v>0</v>
       </c>
@@ -2748,7 +2754,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A142" s="7">
         <v>1</v>
       </c>
@@ -2764,7 +2770,7 @@
       </c>
       <c r="F142" s="9"/>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A143" s="7">
         <v>2</v>
       </c>
@@ -2782,7 +2788,7 @@
       </c>
       <c r="F143" s="9"/>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A144" s="7">
         <v>3</v>
       </c>
@@ -2800,7 +2806,7 @@
       </c>
       <c r="F144" s="9"/>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A145" s="7">
         <v>4</v>
       </c>
@@ -2816,7 +2822,7 @@
       <c r="E145" s="8"/>
       <c r="F145" s="9"/>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A146" s="7">
         <v>5</v>
       </c>
@@ -2832,7 +2838,7 @@
       </c>
       <c r="F146" s="9"/>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A147" s="7">
         <v>6</v>
       </c>
@@ -2850,7 +2856,7 @@
       </c>
       <c r="F147" s="9"/>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A148" s="7">
         <v>7</v>
       </c>
@@ -2868,7 +2874,7 @@
       </c>
       <c r="F148" s="9"/>
     </row>
-    <row r="149" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A149" s="7">
         <v>8</v>
       </c>
@@ -2883,6 +2889,74 @@
         <v>72</v>
       </c>
       <c r="F149" s="9"/>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A151" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A152" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A153" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B153" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C153" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D153" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E153" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F153" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A154" s="7">
+        <v>1</v>
+      </c>
+      <c r="B154" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C154" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D154" s="7"/>
+      <c r="E154" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F154" s="9"/>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A155" s="7">
+        <v>2</v>
+      </c>
+      <c r="B155" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C155" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D155" s="7"/>
+      <c r="E155" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F155" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/documentacion/DD Proyecto.xlsx
+++ b/documentacion/DD Proyecto.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shavi\Downloads\visual\Proyecto\RBE\documentacion\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\52664\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E547348D-FC27-4FAE-B3C3-43DCEE78012F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4815E627-5002-46DB-B3AA-B5AD56A6A790}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13656" yWindow="0" windowWidth="9480" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DICCIONARIO DE DATOS" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="197">
   <si>
     <t>Número</t>
   </si>
@@ -362,12 +362,6 @@
     <t>Es el numero de asientos del modelo de autobus</t>
   </si>
   <si>
-    <t>Es la capacidad del modelo de autobus</t>
-  </si>
-  <si>
-    <t>Es el año del modelo del modelo de autobus</t>
-  </si>
-  <si>
     <t>Es el modelo de cada autobus</t>
   </si>
   <si>
@@ -386,32 +380,20 @@
     <t>Es el numero de licencia del conductor</t>
   </si>
   <si>
-    <t>Es la fecha de contrato para cada conductor</t>
-  </si>
-  <si>
     <t>Es la fecha de vencimiento de licencia del conductor</t>
   </si>
   <si>
     <t>Es el codigo que identifica el tipo de asiento</t>
-  </si>
-  <si>
-    <t>Es el numero de asiento del autobus</t>
   </si>
   <si>
     <t>NOT NULL
 UNIQUE</t>
   </si>
   <si>
-    <t>Es para identificar los tipos de asiento disponibles</t>
-  </si>
-  <si>
     <t>Es el numero que identifica el tipo de pasajero</t>
   </si>
   <si>
     <t>Tiene que estar en el rango del 0 - 100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Concepto del pasajero, puede ser: </t>
   </si>
   <si>
     <t>Es el numero que identifica el tipo de pago</t>
@@ -446,6 +428,210 @@
   </si>
   <si>
     <t>Booleano</t>
+  </si>
+  <si>
+    <t>Codigo identificador unico de marca</t>
+  </si>
+  <si>
+    <t>Es el nombre de la marca del autobus</t>
+  </si>
+  <si>
+    <t>Identificador unico del conductor</t>
+  </si>
+  <si>
+    <t>Es la fecha en la que el conductor inicio el contrato</t>
+  </si>
+  <si>
+    <t>Es para identificar los tipos de asiento disponibles y descripcion de este</t>
+  </si>
+  <si>
+    <t>Concepto del pasajero, puede ser: Niño, adulto y adultos mayores</t>
+  </si>
+  <si>
+    <t>Es el nombre del metodo de pago</t>
+  </si>
+  <si>
+    <t>Es la descripcion del metodo de pago</t>
+  </si>
+  <si>
+    <t>Es el numero identificador del estado del viaje</t>
+  </si>
+  <si>
+    <t>Es el nombre del estado del viaje</t>
+  </si>
+  <si>
+    <t>Descripcion del estado del viaje, puede ser: disponible, en ruta</t>
+  </si>
+  <si>
+    <t>Identificador unico del pasajero</t>
+  </si>
+  <si>
+    <t>Es el nombre de pila del pasajero</t>
+  </si>
+  <si>
+    <t>Es el primer apellido del pasajero</t>
+  </si>
+  <si>
+    <t>Es el segundo apellido del pasajero</t>
+  </si>
+  <si>
+    <t>Es la fecha de nacimiento del pasajero</t>
+  </si>
+  <si>
+    <t>Edad calculada</t>
+  </si>
+  <si>
+    <t>Es la capacidad total en pasajeros del modelo de autobus</t>
+  </si>
+  <si>
+    <t>Es el año de fabricacion del modelo del modelo de autobus</t>
+  </si>
+  <si>
+    <t>Es la marca del autobus, se relaciona con la tabla MARCA</t>
+  </si>
+  <si>
+    <t>Numero identificador de terminal</t>
+  </si>
+  <si>
+    <t>Es el nombre de la terminal</t>
+  </si>
+  <si>
+    <t>Es la calle de la direccion de la terminal</t>
+  </si>
+  <si>
+    <t>Es la colonia de la direccion de la terminal</t>
+  </si>
+  <si>
+    <t>Es el numero de la direccion de la terminal</t>
+  </si>
+  <si>
+    <t>Es la ciudad a la que pertenece la terminal, se relaciona con la tabla CIUDAD</t>
+  </si>
+  <si>
+    <t>Es el codigo identificador de la ruta</t>
+  </si>
+  <si>
+    <t>Es la duracion de la ruta</t>
+  </si>
+  <si>
+    <t>Es la terminal de origen de la ruta, se relaciona con la tabla TERMINAL</t>
+  </si>
+  <si>
+    <t>Es la terminal de destino de la ruta, se relaciona con la tabla TERMINAL</t>
+  </si>
+  <si>
+    <t>Es el numero identificador de cada autobus</t>
+  </si>
+  <si>
+    <t>Es el numero VIN del autobus</t>
+  </si>
+  <si>
+    <t>Es el numero identificador del viaje</t>
+  </si>
+  <si>
+    <t>Es la fecha y hora de salida del viaje</t>
+  </si>
+  <si>
+    <t>Es la fecha y hora de llegada del viaje</t>
+  </si>
+  <si>
+    <t>Es la ruta asignada para el viaje, se relaciona con la tabla RUTA</t>
+  </si>
+  <si>
+    <t>Es el estado del viaje, se relaciona con la tabla EDO_VIAJE</t>
+  </si>
+  <si>
+    <t>Es el autobus asignado para el viaje, se relaciona con la tabla AUTOBUS</t>
+  </si>
+  <si>
+    <t>Es el conductor asignado para el viaje, se relaciona con la tabla CONDUCTOR</t>
+  </si>
+  <si>
+    <t>Es el numero unico de asiento del autobus</t>
+  </si>
+  <si>
+    <t>Es el tipo de asiento, se relaciona con la tabla TIPO_ASIENTO</t>
+  </si>
+  <si>
+    <t>Es el autobus al que pertenece el asiento, se relaciona con la tabla AUTOBUS</t>
+  </si>
+  <si>
+    <t>Controlar asientos ocupados o libres por viaje.</t>
+  </si>
+  <si>
+    <t>Es el numero de asiento, se relaciona con la tabla ASIENTO</t>
+  </si>
+  <si>
+    <t>Es el estado del asiento</t>
+  </si>
+  <si>
+    <t>Es el viaje al que pertenece el asiento, se relaciona con la tabla VIAJE</t>
+  </si>
+  <si>
+    <t>Es el codigo de registro unico del taquillero</t>
+  </si>
+  <si>
+    <t>Es el nombre de pila del taquillero</t>
+  </si>
+  <si>
+    <t>Es el primer apellido del taquillero</t>
+  </si>
+  <si>
+    <t>Es el segundo apellido del taquillero</t>
+  </si>
+  <si>
+    <t>Es la fecha de ingreso del contrato del taquillero</t>
+  </si>
+  <si>
+    <t>Es el usuario del sistema del taquillero</t>
+  </si>
+  <si>
+    <t>Es la contraseña del taquillero</t>
+  </si>
+  <si>
+    <t>Es la terminal en la que labora el taquillero, se relaciona con la tabla TERMINAL</t>
+  </si>
+  <si>
+    <t>Es el numero identificador de pago</t>
+  </si>
+  <si>
+    <t>Es la fecha del pago</t>
+  </si>
+  <si>
+    <t>Es el monto pagado del pago</t>
+  </si>
+  <si>
+    <t>Es el tipo de pago del pago, se relaciona con la tabla TIPO_PAGO</t>
+  </si>
+  <si>
+    <t>Es el taquillero que realizo la venta, se relaciona con la tabla TAQUILLERO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Es el precio final del ticket </t>
+  </si>
+  <si>
+    <t>Es el codigo identificador del ticket</t>
+  </si>
+  <si>
+    <t>Es la fecha en que se genero el ticket</t>
+  </si>
+  <si>
+    <t>Es el viaje que se le asigno al ticket, se relaciona con la tabla VIAJE</t>
+  </si>
+  <si>
+    <t>Es el asiento asignado para el ticket, se relaciona con la tabla ASIENTO</t>
+  </si>
+  <si>
+    <t>Es el pasajero asignado al ticket, se relaciona con la tabla PASAJERO</t>
+  </si>
+  <si>
+    <t>Es el tipo de pasajero asignado al ticket, se relaciona con la tabla TIPO_PASAJERO</t>
+  </si>
+  <si>
+    <t>Es el pago asociado la ticket, se relaciona con la tabla PAGO</t>
+  </si>
+  <si>
+    <t>Almacena las marcas de los autobuses registrados en la empresa.</t>
   </si>
 </sst>
 </file>
@@ -877,32 +1063,34 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A4:G156"/>
-  <sheetFormatPr defaultColWidth="11.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.109375" style="2"/>
-    <col min="2" max="2" width="16.6640625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="16.21875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="12.21875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="12.88671875" style="3" customWidth="1"/>
-    <col min="6" max="6" width="33.33203125" style="12" customWidth="1"/>
-    <col min="7" max="16384" width="11.109375" style="2"/>
+    <col min="1" max="1" width="11.08984375" style="2"/>
+    <col min="2" max="2" width="16.6328125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="16.1796875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="12.1796875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="12.90625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="33.36328125" style="12" customWidth="1"/>
+    <col min="7" max="16384" width="11.08984375" style="2"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="10" t="s">
         <v>66</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="B5"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
@@ -922,12 +1110,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="6">
         <v>1</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>59</v>
@@ -936,9 +1124,11 @@
       <c r="E7" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="11"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F7" s="11" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="6">
         <v>2</v>
       </c>
@@ -954,12 +1144,14 @@
       <c r="E8" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="F8" s="11"/>
+      <c r="F8" s="11" t="s">
+        <v>130</v>
+      </c>
       <c r="G8" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="10" t="s">
         <v>66</v>
       </c>
@@ -967,7 +1159,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="10" t="s">
         <v>83</v>
       </c>
@@ -975,7 +1167,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
         <v>0</v>
       </c>
@@ -995,7 +1187,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="6">
         <v>1</v>
       </c>
@@ -1009,9 +1201,11 @@
       <c r="E13" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="F13" s="11"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F13" s="11" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="6">
         <v>2</v>
       </c>
@@ -1028,10 +1222,10 @@
         <v>64</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="6">
         <v>3</v>
       </c>
@@ -1048,10 +1242,10 @@
         <v>64</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="6">
         <v>4</v>
       </c>
@@ -1066,10 +1260,10 @@
       </c>
       <c r="E16" s="7"/>
       <c r="F16" s="11" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" s="6">
         <v>5</v>
       </c>
@@ -1086,10 +1280,10 @@
         <v>64</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A18" s="6">
         <v>6</v>
       </c>
@@ -1104,10 +1298,10 @@
         <v>64</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A19" s="6">
         <v>7</v>
       </c>
@@ -1122,13 +1316,13 @@
         <v>64</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="G19" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="10" t="s">
         <v>66</v>
       </c>
@@ -1136,7 +1330,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="10" t="s">
         <v>83</v>
       </c>
@@ -1144,7 +1338,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
         <v>0</v>
       </c>
@@ -1164,7 +1358,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" s="6">
         <v>1</v>
       </c>
@@ -1184,7 +1378,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" s="6">
         <v>2</v>
       </c>
@@ -1207,7 +1401,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" s="10" t="s">
         <v>66</v>
       </c>
@@ -1215,7 +1409,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" s="10" t="s">
         <v>83</v>
       </c>
@@ -1223,7 +1417,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
         <v>0</v>
       </c>
@@ -1243,7 +1437,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A30" s="6">
         <v>1</v>
       </c>
@@ -1260,10 +1454,10 @@
         <v>7</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A31" s="6">
         <v>2</v>
       </c>
@@ -1277,16 +1471,16 @@
         <v>30</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="G31" s="2">
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" s="10" t="s">
         <v>66</v>
       </c>
@@ -1294,7 +1488,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" s="10" t="s">
         <v>83</v>
       </c>
@@ -1302,7 +1496,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
         <v>0</v>
       </c>
@@ -1322,7 +1516,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A36" s="6">
         <v>1</v>
       </c>
@@ -1337,10 +1531,10 @@
         <v>7</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" s="6">
         <v>2</v>
       </c>
@@ -1355,10 +1549,10 @@
         <v>64</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A38" s="6">
         <v>3</v>
       </c>
@@ -1372,16 +1566,16 @@
         <v>30</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="G38" s="2">
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" s="10" t="s">
         <v>66</v>
       </c>
@@ -1389,7 +1583,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" s="10" t="s">
         <v>83</v>
       </c>
@@ -1397,7 +1591,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="s">
         <v>0</v>
       </c>
@@ -1417,7 +1611,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A43" s="6">
         <v>1</v>
       </c>
@@ -1432,10 +1626,10 @@
         <v>7</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" s="6">
         <v>2</v>
       </c>
@@ -1451,9 +1645,11 @@
       <c r="E44" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="F44" s="11"/>
-    </row>
-    <row r="45" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="F44" s="11" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A45" s="6">
         <v>3</v>
       </c>
@@ -1467,14 +1663,16 @@
         <v>50</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="F45" s="11"/>
+        <v>115</v>
+      </c>
+      <c r="F45" s="11" t="s">
+        <v>136</v>
+      </c>
       <c r="G45" s="2">
         <v>6</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" s="10" t="s">
         <v>66</v>
       </c>
@@ -1482,7 +1680,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48" s="10" t="s">
         <v>83</v>
       </c>
@@ -1490,7 +1688,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49" s="4" t="s">
         <v>0</v>
       </c>
@@ -1510,7 +1708,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A50" s="6">
         <v>1</v>
       </c>
@@ -1528,7 +1726,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51" s="6">
         <v>2</v>
       </c>
@@ -1548,7 +1746,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A52" s="6">
         <v>3</v>
       </c>
@@ -1566,7 +1764,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A53" s="6">
         <v>4</v>
       </c>
@@ -1581,10 +1779,10 @@
         <v>64</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A54" s="6">
         <v>5</v>
       </c>
@@ -1599,10 +1797,10 @@
         <v>64</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A55" s="6">
         <v>6</v>
       </c>
@@ -1614,14 +1812,16 @@
       </c>
       <c r="D55" s="6"/>
       <c r="E55" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="F55" s="11"/>
+        <v>121</v>
+      </c>
+      <c r="F55" s="11" t="s">
+        <v>148</v>
+      </c>
       <c r="G55" s="2">
         <v>7</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57" s="10" t="s">
         <v>66</v>
       </c>
@@ -1629,7 +1829,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58" s="10" t="s">
         <v>83</v>
       </c>
@@ -1637,7 +1837,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59" s="4" t="s">
         <v>0</v>
       </c>
@@ -1657,7 +1857,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A60" s="6">
         <v>1</v>
       </c>
@@ -1671,9 +1871,11 @@
       <c r="E60" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="F60" s="11"/>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F60" s="11" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A61" s="6">
         <v>2</v>
       </c>
@@ -1689,9 +1891,11 @@
       <c r="E61" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="F61" s="11"/>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F61" s="11" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A62" s="6">
         <v>3</v>
       </c>
@@ -1707,12 +1911,14 @@
       <c r="E62" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="F62" s="11"/>
+      <c r="F62" s="11" t="s">
+        <v>139</v>
+      </c>
       <c r="G62" s="2">
         <v>8</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A64" s="10" t="s">
         <v>66</v>
       </c>
@@ -1720,7 +1926,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A65" s="10" t="s">
         <v>83</v>
       </c>
@@ -1728,7 +1934,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A66" s="4" t="s">
         <v>0</v>
       </c>
@@ -1748,7 +1954,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A67" s="6">
         <v>1</v>
       </c>
@@ -1762,9 +1968,11 @@
       <c r="E67" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="F67" s="11"/>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F67" s="11" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68" s="6">
         <v>2</v>
       </c>
@@ -1780,14 +1988,16 @@
       <c r="E68" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="F68" s="11"/>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F68" s="11" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A69" s="6">
         <v>3</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="C69" s="6" t="s">
         <v>61</v>
@@ -1798,14 +2008,16 @@
       <c r="E69" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="F69" s="11"/>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F69" s="11" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A70" s="6">
         <v>4</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C70" s="6" t="s">
         <v>61</v>
@@ -1816,14 +2028,16 @@
       <c r="E70" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="F70" s="11"/>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F70" s="11" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A71" s="6">
         <v>5</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="C71" s="6" t="s">
         <v>61</v>
@@ -1834,9 +2048,11 @@
       <c r="E71" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="F71" s="11"/>
-    </row>
-    <row r="72" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="F71" s="11" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A72" s="6">
         <v>6</v>
       </c>
@@ -1852,12 +2068,14 @@
       <c r="E72" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="F72" s="11"/>
+      <c r="F72" s="11" t="s">
+        <v>154</v>
+      </c>
       <c r="G72" s="2">
         <v>9</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A74" s="10" t="s">
         <v>66</v>
       </c>
@@ -1865,7 +2083,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A75" s="10" t="s">
         <v>83</v>
       </c>
@@ -1873,7 +2091,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A76" s="4" t="s">
         <v>0</v>
       </c>
@@ -1893,7 +2111,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="77" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A77" s="6">
         <v>1</v>
       </c>
@@ -1907,9 +2125,11 @@
       <c r="E77" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="F77" s="11"/>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F77" s="11" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A78" s="6">
         <v>2</v>
       </c>
@@ -1925,9 +2145,11 @@
       <c r="E78" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="F78" s="11"/>
-    </row>
-    <row r="79" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="F78" s="11" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A79" s="6">
         <v>3</v>
       </c>
@@ -1941,9 +2163,11 @@
       <c r="E79" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="F79" s="11"/>
-    </row>
-    <row r="80" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="F79" s="11" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A80" s="6">
         <v>4</v>
       </c>
@@ -1957,12 +2181,14 @@
       <c r="E80" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="F80" s="11"/>
+      <c r="F80" s="11" t="s">
+        <v>158</v>
+      </c>
       <c r="G80" s="2">
         <v>10</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A82" s="10" t="s">
         <v>66</v>
       </c>
@@ -1970,7 +2196,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A83" s="10" t="s">
         <v>83</v>
       </c>
@@ -1978,7 +2204,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A84" s="4" t="s">
         <v>0</v>
       </c>
@@ -1998,7 +2224,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="85" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A85" s="6">
         <v>1</v>
       </c>
@@ -2012,14 +2238,16 @@
       <c r="E85" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="F85" s="11"/>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F85" s="11" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A86" s="6">
         <v>2</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="C86" s="6" t="s">
         <v>101</v>
@@ -2028,14 +2256,16 @@
       <c r="E86" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="F86" s="11"/>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F86" s="11" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A87" s="6">
         <v>3</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="C87" s="6" t="s">
         <v>101</v>
@@ -2044,9 +2274,11 @@
       <c r="E87" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="F87" s="11"/>
-    </row>
-    <row r="88" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="F87" s="11" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A88" s="6">
         <v>4</v>
       </c>
@@ -2060,9 +2292,11 @@
       <c r="E88" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="F88" s="11"/>
-    </row>
-    <row r="89" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="F88" s="11" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A89" s="6">
         <v>5</v>
       </c>
@@ -2076,12 +2310,14 @@
       <c r="E89" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="F89" s="11"/>
+      <c r="F89" s="11" t="s">
+        <v>165</v>
+      </c>
       <c r="G89" s="2">
         <v>11</v>
       </c>
     </row>
-    <row r="90" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A90" s="6">
         <v>6</v>
       </c>
@@ -2095,9 +2331,11 @@
       <c r="E90" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="F90" s="11"/>
-    </row>
-    <row r="91" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="F90" s="11" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A91" s="6">
         <v>7</v>
       </c>
@@ -2111,9 +2349,11 @@
       <c r="E91" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="F91" s="11"/>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F91" s="11" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A93" s="10" t="s">
         <v>66</v>
       </c>
@@ -2121,7 +2361,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A94" s="10" t="s">
         <v>83</v>
       </c>
@@ -2129,7 +2369,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A95" s="4" t="s">
         <v>0</v>
       </c>
@@ -2149,7 +2389,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A96" s="6">
         <v>1</v>
       </c>
@@ -2163,9 +2403,11 @@
       <c r="E96" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="F96" s="11"/>
-    </row>
-    <row r="97" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="F96" s="11" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A97" s="6">
         <v>2</v>
       </c>
@@ -2180,10 +2422,10 @@
         <v>63</v>
       </c>
       <c r="F97" s="11" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A98" s="6">
         <v>3</v>
       </c>
@@ -2200,15 +2442,15 @@
         <v>65</v>
       </c>
       <c r="F98" s="11" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A99" s="6">
         <v>4</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C99" s="6" t="s">
         <v>61</v>
@@ -2220,13 +2462,13 @@
         <v>65</v>
       </c>
       <c r="F99" s="11" t="s">
-        <v>110</v>
+        <v>160</v>
       </c>
       <c r="G99" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A101" s="10" t="s">
         <v>66</v>
       </c>
@@ -2234,7 +2476,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A102" s="10" t="s">
         <v>83</v>
       </c>
@@ -2242,7 +2484,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A103" s="4" t="s">
         <v>0</v>
       </c>
@@ -2262,7 +2504,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="104" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A104" s="6">
         <v>1</v>
       </c>
@@ -2277,10 +2519,10 @@
         <v>84</v>
       </c>
       <c r="F104" s="11" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A105" s="6">
         <v>2</v>
       </c>
@@ -2296,9 +2538,11 @@
       <c r="E105" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="F105" s="11"/>
-    </row>
-    <row r="106" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="F105" s="11" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A106" s="6">
         <v>3</v>
       </c>
@@ -2312,26 +2556,30 @@
       <c r="E106" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="F106" s="11"/>
+      <c r="F106" s="11" t="s">
+        <v>170</v>
+      </c>
       <c r="G106" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A108" s="10" t="s">
         <v>66</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A109" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="B109" s="1"/>
-    </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B109" s="1" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A110" s="4" t="s">
         <v>0</v>
       </c>
@@ -2351,7 +2599,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A111" s="6">
         <v>1</v>
       </c>
@@ -2365,9 +2613,11 @@
       <c r="E111" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F111" s="11"/>
-    </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F111" s="11" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A112" s="6">
         <v>2</v>
       </c>
@@ -2381,9 +2631,11 @@
       <c r="E112" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F112" s="11"/>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F112" s="11" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A113" s="6">
         <v>3</v>
       </c>
@@ -2391,18 +2643,20 @@
         <v>37</v>
       </c>
       <c r="C113" s="6" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="D113" s="6"/>
       <c r="E113" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="F113" s="11"/>
+      <c r="F113" s="11" t="s">
+        <v>173</v>
+      </c>
       <c r="G113" s="2">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A115" s="10" t="s">
         <v>66</v>
       </c>
@@ -2410,7 +2664,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A116" s="10" t="s">
         <v>83</v>
       </c>
@@ -2418,7 +2672,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A117" s="4" t="s">
         <v>0</v>
       </c>
@@ -2438,7 +2692,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="118" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A118" s="6">
         <v>1</v>
       </c>
@@ -2452,9 +2706,11 @@
       <c r="E118" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="F118" s="11"/>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F118" s="11" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A119" s="6">
         <v>2</v>
       </c>
@@ -2470,9 +2726,11 @@
       <c r="E119" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="F119" s="11"/>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F119" s="11" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A120" s="6">
         <v>3</v>
       </c>
@@ -2488,9 +2746,11 @@
       <c r="E120" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="F120" s="11"/>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F120" s="11" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A121" s="6">
         <v>4</v>
       </c>
@@ -2504,9 +2764,11 @@
         <v>30</v>
       </c>
       <c r="E121" s="7"/>
-      <c r="F121" s="11"/>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F121" s="11" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A122" s="6">
         <v>5</v>
       </c>
@@ -2520,9 +2782,11 @@
       <c r="E122" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="F122" s="11"/>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F122" s="11" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A123" s="6">
         <v>6</v>
       </c>
@@ -2534,12 +2798,14 @@
       </c>
       <c r="D123" s="6"/>
       <c r="E123" s="7"/>
-      <c r="F123" s="11"/>
+      <c r="F123" s="11" t="s">
+        <v>145</v>
+      </c>
       <c r="G123" s="2">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A125" s="10" t="s">
         <v>66</v>
       </c>
@@ -2547,7 +2813,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A126" s="10" t="s">
         <v>83</v>
       </c>
@@ -2555,7 +2821,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A127" s="4" t="s">
         <v>0</v>
       </c>
@@ -2575,7 +2841,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="128" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A128" s="6">
         <v>1</v>
       </c>
@@ -2589,9 +2855,11 @@
       <c r="E128" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="F128" s="11"/>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F128" s="11" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A129" s="6">
         <v>2</v>
       </c>
@@ -2605,9 +2873,11 @@
       <c r="E129" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="F129" s="11"/>
-    </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F129" s="11" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A130" s="6">
         <v>3</v>
       </c>
@@ -2621,9 +2891,11 @@
       <c r="E130" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="F130" s="11"/>
-    </row>
-    <row r="131" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="F130" s="11" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A131" s="6">
         <v>4</v>
       </c>
@@ -2637,9 +2909,11 @@
       <c r="E131" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="F131" s="11"/>
-    </row>
-    <row r="132" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="F131" s="11" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A132" s="6">
         <v>5</v>
       </c>
@@ -2653,12 +2927,14 @@
       <c r="E132" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="F132" s="11"/>
+      <c r="F132" s="11" t="s">
+        <v>187</v>
+      </c>
       <c r="G132" s="2">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A134" s="10" t="s">
         <v>66</v>
       </c>
@@ -2666,7 +2942,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A135" s="10" t="s">
         <v>83</v>
       </c>
@@ -2674,7 +2950,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A136" s="4" t="s">
         <v>0</v>
       </c>
@@ -2694,7 +2970,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="137" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A137" s="6">
         <v>1</v>
       </c>
@@ -2708,9 +2984,11 @@
       <c r="E137" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="F137" s="11"/>
-    </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F137" s="11" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A138" s="6">
         <v>2</v>
       </c>
@@ -2724,9 +3002,11 @@
       <c r="E138" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="F138" s="11"/>
-    </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F138" s="11" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A139" s="6">
         <v>3</v>
       </c>
@@ -2740,9 +3020,11 @@
       <c r="E139" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="F139" s="11"/>
-    </row>
-    <row r="140" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="F139" s="11" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A140" s="6">
         <v>4</v>
       </c>
@@ -2756,9 +3038,11 @@
       <c r="E140" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="F140" s="11"/>
-    </row>
-    <row r="141" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="F140" s="11" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A141" s="6">
         <v>5</v>
       </c>
@@ -2772,9 +3056,11 @@
       <c r="E141" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="F141" s="11"/>
-    </row>
-    <row r="142" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="F141" s="11" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A142" s="6">
         <v>6</v>
       </c>
@@ -2788,9 +3074,11 @@
       <c r="E142" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="F142" s="11"/>
-    </row>
-    <row r="143" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="F142" s="11" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A143" s="6">
         <v>7</v>
       </c>
@@ -2804,9 +3092,11 @@
       <c r="E143" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="F143" s="11"/>
-    </row>
-    <row r="144" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="F143" s="11" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A144" s="6">
         <v>8</v>
       </c>
@@ -2820,12 +3110,14 @@
       <c r="E144" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="F144" s="11"/>
+      <c r="F144" s="11" t="s">
+        <v>195</v>
+      </c>
       <c r="G144" s="2">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A146" s="10" t="s">
         <v>66</v>
       </c>
@@ -2833,7 +3125,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A147" s="10" t="s">
         <v>83</v>
       </c>
@@ -2841,7 +3133,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A148" s="4" t="s">
         <v>0</v>
       </c>
@@ -2861,7 +3153,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A149" s="6">
         <v>1</v>
       </c>
@@ -2875,9 +3167,11 @@
       <c r="E149" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="F149" s="11"/>
-    </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F149" s="11" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A150" s="6">
         <v>2</v>
       </c>
@@ -2893,9 +3187,11 @@
       <c r="E150" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="F150" s="11"/>
-    </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F150" s="11" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A151" s="6">
         <v>3</v>
       </c>
@@ -2911,9 +3207,11 @@
       <c r="E151" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="F151" s="11"/>
-    </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F151" s="11" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A152" s="6">
         <v>4</v>
       </c>
@@ -2927,9 +3225,11 @@
         <v>30</v>
       </c>
       <c r="E152" s="7"/>
-      <c r="F152" s="11"/>
-    </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F152" s="11" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A153" s="6">
         <v>5</v>
       </c>
@@ -2943,9 +3243,11 @@
       <c r="E153" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="F153" s="11"/>
-    </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F153" s="11" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A154" s="6">
         <v>6</v>
       </c>
@@ -2961,9 +3263,11 @@
       <c r="E154" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="F154" s="11"/>
-    </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F154" s="11" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A155" s="6">
         <v>7</v>
       </c>
@@ -2979,9 +3283,11 @@
       <c r="E155" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="F155" s="11"/>
-    </row>
-    <row r="156" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="F155" s="11" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A156" s="6">
         <v>8</v>
       </c>
@@ -2995,9 +3301,11 @@
       <c r="E156" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="F156" s="11"/>
+      <c r="F156" s="11" t="s">
+        <v>182</v>
+      </c>
       <c r="G156" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/documentacion/DD Proyecto.xlsx
+++ b/documentacion/DD Proyecto.xlsx
@@ -5,18 +5,18 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\52664\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shavi\Downloads\visual\Proyecto\RBE\documentacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4815E627-5002-46DB-B3AA-B5AD56A6A790}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D90EE08-E5EB-494B-A85F-3FC8EE9526D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DICCIONARIO DE DATOS" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'DICCIONARIO DE DATOS'!$A$1:$F$156</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'DICCIONARIO DE DATOS'!$A$1:$F$157</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="201">
   <si>
     <t>Número</t>
   </si>
@@ -632,6 +632,19 @@
   </si>
   <si>
     <t>Almacena las marcas de los autobuses registrados en la empresa.</t>
+  </si>
+  <si>
+    <t>costo</t>
+  </si>
+  <si>
+    <t>decimal</t>
+  </si>
+  <si>
+    <t>NOT NULL
+DEFAULT</t>
+  </si>
+  <si>
+    <t>Es el coste de la ruta por ticket para luego calcular el costo del ticket, con valor por defecto de 250</t>
   </si>
 </sst>
 </file>
@@ -1062,19 +1075,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A4:G156"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A4:G157"/>
+  <sheetFormatPr defaultColWidth="11.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.08984375" style="2"/>
-    <col min="2" max="2" width="16.6328125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="16.1796875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="12.1796875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="12.90625" style="3" customWidth="1"/>
-    <col min="6" max="6" width="33.36328125" style="12" customWidth="1"/>
-    <col min="7" max="16384" width="11.08984375" style="2"/>
+    <col min="1" max="1" width="11.109375" style="2"/>
+    <col min="2" max="2" width="16.6640625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="16.21875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="12.21875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="12.88671875" style="3" customWidth="1"/>
+    <col min="6" max="6" width="33.33203125" style="12" customWidth="1"/>
+    <col min="7" max="16384" width="11.109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
         <v>66</v>
       </c>
@@ -1082,7 +1095,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>83</v>
       </c>
@@ -1090,7 +1103,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
@@ -1110,7 +1123,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="6">
         <v>1</v>
       </c>
@@ -1128,7 +1141,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="6">
         <v>2</v>
       </c>
@@ -1151,7 +1164,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="10" t="s">
         <v>66</v>
       </c>
@@ -1159,7 +1172,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
         <v>83</v>
       </c>
@@ -1167,7 +1180,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>0</v>
       </c>
@@ -1187,7 +1200,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="6">
         <v>1</v>
       </c>
@@ -1205,7 +1218,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="6">
         <v>2</v>
       </c>
@@ -1225,7 +1238,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="6">
         <v>3</v>
       </c>
@@ -1245,7 +1258,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="6">
         <v>4</v>
       </c>
@@ -1263,7 +1276,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="6">
         <v>5</v>
       </c>
@@ -1283,7 +1296,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="6">
         <v>6</v>
       </c>
@@ -1301,7 +1314,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="6">
         <v>7</v>
       </c>
@@ -1322,7 +1335,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
         <v>66</v>
       </c>
@@ -1330,7 +1343,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="10" t="s">
         <v>83</v>
       </c>
@@ -1338,7 +1351,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>0</v>
       </c>
@@ -1358,7 +1371,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="6">
         <v>1</v>
       </c>
@@ -1378,7 +1391,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="6">
         <v>2</v>
       </c>
@@ -1401,7 +1414,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
         <v>66</v>
       </c>
@@ -1409,7 +1422,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="10" t="s">
         <v>83</v>
       </c>
@@ -1417,7 +1430,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>0</v>
       </c>
@@ -1437,7 +1450,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A30" s="6">
         <v>1</v>
       </c>
@@ -1457,7 +1470,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A31" s="6">
         <v>2</v>
       </c>
@@ -1480,7 +1493,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="10" t="s">
         <v>66</v>
       </c>
@@ -1488,7 +1501,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="10" t="s">
         <v>83</v>
       </c>
@@ -1496,7 +1509,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>0</v>
       </c>
@@ -1516,7 +1529,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A36" s="6">
         <v>1</v>
       </c>
@@ -1534,7 +1547,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="6">
         <v>2</v>
       </c>
@@ -1552,7 +1565,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A38" s="6">
         <v>3</v>
       </c>
@@ -1575,7 +1588,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="10" t="s">
         <v>66</v>
       </c>
@@ -1583,7 +1596,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="10" t="s">
         <v>83</v>
       </c>
@@ -1591,7 +1604,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
         <v>0</v>
       </c>
@@ -1611,7 +1624,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A43" s="6">
         <v>1</v>
       </c>
@@ -1629,7 +1642,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="6">
         <v>2</v>
       </c>
@@ -1649,7 +1662,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A45" s="6">
         <v>3</v>
       </c>
@@ -1672,7 +1685,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="10" t="s">
         <v>66</v>
       </c>
@@ -1680,7 +1693,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="10" t="s">
         <v>83</v>
       </c>
@@ -1688,7 +1701,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
         <v>0</v>
       </c>
@@ -1708,7 +1721,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A50" s="6">
         <v>1</v>
       </c>
@@ -1726,7 +1739,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" s="6">
         <v>2</v>
       </c>
@@ -1746,7 +1759,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A52" s="6">
         <v>3</v>
       </c>
@@ -1764,7 +1777,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A53" s="6">
         <v>4</v>
       </c>
@@ -1782,7 +1795,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A54" s="6">
         <v>5</v>
       </c>
@@ -1800,7 +1813,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A55" s="6">
         <v>6</v>
       </c>
@@ -1821,7 +1834,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" s="10" t="s">
         <v>66</v>
       </c>
@@ -1829,7 +1842,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" s="10" t="s">
         <v>83</v>
       </c>
@@ -1837,7 +1850,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
         <v>0</v>
       </c>
@@ -1857,7 +1870,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A60" s="6">
         <v>1</v>
       </c>
@@ -1875,7 +1888,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" s="6">
         <v>2</v>
       </c>
@@ -1895,7 +1908,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A62" s="6">
         <v>3</v>
       </c>
@@ -1918,7 +1931,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" s="10" t="s">
         <v>66</v>
       </c>
@@ -1926,7 +1939,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" s="10" t="s">
         <v>83</v>
       </c>
@@ -1934,7 +1947,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" s="4" t="s">
         <v>0</v>
       </c>
@@ -1954,7 +1967,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" s="6">
         <v>1</v>
       </c>
@@ -1972,7 +1985,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" s="6">
         <v>2</v>
       </c>
@@ -1992,7 +2005,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" s="6">
         <v>3</v>
       </c>
@@ -2012,7 +2025,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="70" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A70" s="6">
         <v>4</v>
       </c>
@@ -2032,7 +2045,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="71" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A71" s="6">
         <v>5</v>
       </c>
@@ -2043,7 +2056,7 @@
         <v>61</v>
       </c>
       <c r="D71" s="6">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E71" s="7" t="s">
         <v>64</v>
@@ -2052,127 +2065,129 @@
         <v>152</v>
       </c>
     </row>
-    <row r="72" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A72" s="6">
         <v>6</v>
       </c>
       <c r="B72" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="C72" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="D72" s="6">
+        <v>30</v>
+      </c>
+      <c r="E72" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="F72" s="11" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A73" s="6">
+        <v>7</v>
+      </c>
+      <c r="B73" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C72" s="6" t="s">
+      <c r="C73" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="D72" s="6">
+      <c r="D73" s="6">
         <v>5</v>
       </c>
-      <c r="E72" s="7" t="s">
+      <c r="E73" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="F72" s="11" t="s">
+      <c r="F73" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="G72" s="2">
+      <c r="G73" s="2">
         <v>9</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A74" s="10" t="s">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A75" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="B74" s="1" t="s">
+      <c r="B75" s="1" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A75" s="10" t="s">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A76" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="B75" s="1" t="s">
+      <c r="B76" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A76" s="4" t="s">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A77" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B76" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C76" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D76" s="4" t="s">
+      <c r="B77" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D77" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E76" s="5" t="s">
+      <c r="E77" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F76" s="5" t="s">
+      <c r="F77" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="77" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A77" s="6">
-        <v>1</v>
-      </c>
-      <c r="B77" s="6" t="s">
+    <row r="78" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A78" s="6">
+        <v>1</v>
+      </c>
+      <c r="B78" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C77" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="D77" s="6"/>
-      <c r="E77" s="7" t="s">
+      <c r="C78" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D78" s="6"/>
+      <c r="E78" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="F77" s="11" t="s">
+      <c r="F78" s="11" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A78" s="6">
-        <v>2</v>
-      </c>
-      <c r="B78" s="6" t="s">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A79" s="6">
+        <v>2</v>
+      </c>
+      <c r="B79" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C78" s="6" t="s">
+      <c r="C79" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="D78" s="6">
+      <c r="D79" s="6">
         <v>10</v>
       </c>
-      <c r="E78" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="F78" s="11" t="s">
+      <c r="E79" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="F79" s="11" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="79" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A79" s="6">
+    <row r="80" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A80" s="6">
         <v>3</v>
       </c>
-      <c r="B79" s="6" t="s">
+      <c r="B80" s="6" t="s">
         <v>26</v>
-      </c>
-      <c r="C79" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="D79" s="6"/>
-      <c r="E79" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="F79" s="11" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A80" s="6">
-        <v>4</v>
-      </c>
-      <c r="B80" s="6" t="s">
-        <v>27</v>
       </c>
       <c r="C80" s="6" t="s">
         <v>59</v>
@@ -2182,90 +2197,90 @@
         <v>63</v>
       </c>
       <c r="F80" s="11" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A81" s="6">
+        <v>4</v>
+      </c>
+      <c r="B81" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C81" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D81" s="6"/>
+      <c r="E81" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="F81" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="G80" s="2">
+      <c r="G81" s="2">
         <v>10</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A82" s="10" t="s">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A83" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="B82" s="1" t="s">
+      <c r="B83" s="1" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A83" s="10" t="s">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A84" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="B83" s="1" t="s">
+      <c r="B84" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A84" s="4" t="s">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A85" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B84" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C84" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D84" s="4" t="s">
+      <c r="B85" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D85" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E84" s="5" t="s">
+      <c r="E85" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F84" s="5" t="s">
+      <c r="F85" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="85" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A85" s="6">
-        <v>1</v>
-      </c>
-      <c r="B85" s="6" t="s">
+    <row r="86" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A86" s="6">
+        <v>1</v>
+      </c>
+      <c r="B86" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C85" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="D85" s="6"/>
-      <c r="E85" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="F85" s="11" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A86" s="6">
-        <v>2</v>
-      </c>
-      <c r="B86" s="6" t="s">
-        <v>125</v>
-      </c>
       <c r="C86" s="6" t="s">
-        <v>101</v>
+        <v>59</v>
       </c>
       <c r="D86" s="6"/>
       <c r="E86" s="7" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="F86" s="11" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.35">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C87" s="6" t="s">
         <v>101</v>
@@ -2275,33 +2290,33 @@
         <v>64</v>
       </c>
       <c r="F87" s="11" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>29</v>
+        <v>126</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>59</v>
+        <v>101</v>
       </c>
       <c r="D88" s="6"/>
       <c r="E88" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F88" s="11" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A89" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C89" s="6" t="s">
         <v>59</v>
@@ -2311,18 +2326,15 @@
         <v>63</v>
       </c>
       <c r="F89" s="11" t="s">
-        <v>165</v>
-      </c>
-      <c r="G89" s="2">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A90" s="6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C90" s="6" t="s">
         <v>59</v>
@@ -2332,15 +2344,18 @@
         <v>63</v>
       </c>
       <c r="F90" s="11" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>165</v>
+      </c>
+      <c r="G90" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A91" s="6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C91" s="6" t="s">
         <v>59</v>
@@ -2350,279 +2365,279 @@
         <v>63</v>
       </c>
       <c r="F91" s="11" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A92" s="6">
+        <v>7</v>
+      </c>
+      <c r="B92" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C92" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D92" s="6"/>
+      <c r="E92" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="F92" s="11" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A93" s="10" t="s">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A94" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="B93" s="1" t="s">
+      <c r="B94" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A94" s="10" t="s">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A95" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="B94" s="1" t="s">
+      <c r="B95" s="1" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A95" s="4" t="s">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A96" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B95" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C95" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D95" s="4" t="s">
+      <c r="B96" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D96" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E95" s="5" t="s">
+      <c r="E96" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F95" s="5" t="s">
+      <c r="F96" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="96" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A96" s="6">
-        <v>1</v>
-      </c>
-      <c r="B96" s="6" t="s">
+    <row r="97" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A97" s="6">
+        <v>1</v>
+      </c>
+      <c r="B97" s="6" t="s">
         <v>6</v>
-      </c>
-      <c r="C96" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="D96" s="6"/>
-      <c r="E96" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F96" s="11" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A97" s="6">
-        <v>2</v>
-      </c>
-      <c r="B97" s="6" t="s">
-        <v>31</v>
       </c>
       <c r="C97" s="6" t="s">
         <v>59</v>
       </c>
       <c r="D97" s="6"/>
       <c r="E97" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="F97" s="11" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A98" s="6">
+        <v>2</v>
+      </c>
+      <c r="B98" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C98" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D98" s="6"/>
+      <c r="E98" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="F97" s="11" t="s">
+      <c r="F98" s="11" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="98" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A98" s="6">
+    <row r="99" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A99" s="6">
         <v>3</v>
       </c>
-      <c r="B98" s="6" t="s">
+      <c r="B99" s="6" t="s">
         <v>32</v>
-      </c>
-      <c r="C98" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="D98" s="6">
-        <v>10</v>
-      </c>
-      <c r="E98" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="F98" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A99" s="6">
-        <v>4</v>
-      </c>
-      <c r="B99" s="6" t="s">
-        <v>127</v>
       </c>
       <c r="C99" s="6" t="s">
         <v>61</v>
       </c>
       <c r="D99" s="6">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E99" s="7" t="s">
         <v>65</v>
       </c>
       <c r="F99" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A100" s="6">
+        <v>4</v>
+      </c>
+      <c r="B100" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="C100" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D100" s="6">
+        <v>17</v>
+      </c>
+      <c r="E100" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="F100" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="G99" s="2">
+      <c r="G100" s="2">
         <v>12</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A101" s="10" t="s">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A102" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="B101" s="1" t="s">
+      <c r="B102" s="1" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A102" s="10" t="s">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A103" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="B102" s="1" t="s">
+      <c r="B103" s="1" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A103" s="4" t="s">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A104" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B103" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C103" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D103" s="4" t="s">
+      <c r="B104" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C104" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D104" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E103" s="5" t="s">
+      <c r="E104" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F103" s="5" t="s">
+      <c r="F104" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="104" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A104" s="6">
-        <v>1</v>
-      </c>
-      <c r="B104" s="6" t="s">
+    <row r="105" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A105" s="6">
+        <v>1</v>
+      </c>
+      <c r="B105" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C104" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="D104" s="6"/>
-      <c r="E104" s="7" t="s">
+      <c r="C105" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D105" s="6"/>
+      <c r="E105" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="F104" s="11" t="s">
+      <c r="F105" s="11" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="105" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A105" s="6">
-        <v>2</v>
-      </c>
-      <c r="B105" s="6" t="s">
+    <row r="106" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A106" s="6">
+        <v>2</v>
+      </c>
+      <c r="B106" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C105" s="8" t="s">
+      <c r="C106" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="D105" s="6">
+      <c r="D106" s="6">
         <v>5</v>
       </c>
-      <c r="E105" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="F105" s="11" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A106" s="6">
-        <v>3</v>
-      </c>
-      <c r="B106" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C106" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="D106" s="6"/>
       <c r="E106" s="7" t="s">
         <v>63</v>
       </c>
       <c r="F106" s="11" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A107" s="6">
+        <v>3</v>
+      </c>
+      <c r="B107" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C107" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D107" s="6"/>
+      <c r="E107" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="F107" s="11" t="s">
         <v>170</v>
       </c>
-      <c r="G106" s="2">
+      <c r="G107" s="2">
         <v>13</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A108" s="10" t="s">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A109" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="B108" s="1" t="s">
+      <c r="B109" s="1" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A109" s="10" t="s">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A110" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="B109" s="1" t="s">
+      <c r="B110" s="1" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A110" s="4" t="s">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A111" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B110" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C110" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D110" s="4" t="s">
+      <c r="B111" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C111" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D111" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E110" s="5" t="s">
+      <c r="E111" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F110" s="5" t="s">
+      <c r="F111" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="111" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A111" s="6">
-        <v>1</v>
-      </c>
-      <c r="B111" s="6" t="s">
+    <row r="112" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A112" s="6">
+        <v>1</v>
+      </c>
+      <c r="B112" s="6" t="s">
         <v>46</v>
-      </c>
-      <c r="C111" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="D111" s="6"/>
-      <c r="E111" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F111" s="11" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="112" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A112" s="6">
-        <v>2</v>
-      </c>
-      <c r="B112" s="6" t="s">
-        <v>35</v>
       </c>
       <c r="C112" s="6" t="s">
         <v>59</v>
@@ -2632,110 +2647,108 @@
         <v>34</v>
       </c>
       <c r="F112" s="11" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.35">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A113" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C113" s="6" t="s">
-        <v>128</v>
+        <v>59</v>
       </c>
       <c r="D113" s="6"/>
       <c r="E113" s="7" t="s">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="F113" s="11" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A114" s="6">
+        <v>3</v>
+      </c>
+      <c r="B114" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C114" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="D114" s="6"/>
+      <c r="E114" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="F114" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="G113" s="2">
+      <c r="G114" s="2">
         <v>14</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A115" s="10" t="s">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A116" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="B115" s="1" t="s">
+      <c r="B116" s="1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A116" s="10" t="s">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A117" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="B116" s="1" t="s">
+      <c r="B117" s="1" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A117" s="4" t="s">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A118" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B117" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C117" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D117" s="4" t="s">
+      <c r="B118" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C118" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D118" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E117" s="5" t="s">
+      <c r="E118" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F117" s="5" t="s">
+      <c r="F118" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="118" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A118" s="6">
-        <v>1</v>
-      </c>
-      <c r="B118" s="6" t="s">
+    <row r="119" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A119" s="6">
+        <v>1</v>
+      </c>
+      <c r="B119" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C118" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="D118" s="6"/>
-      <c r="E118" s="7" t="s">
+      <c r="C119" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D119" s="6"/>
+      <c r="E119" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="F118" s="11" t="s">
+      <c r="F119" s="11" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A119" s="6">
-        <v>2</v>
-      </c>
-      <c r="B119" s="6" t="s">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A120" s="6">
+        <v>2</v>
+      </c>
+      <c r="B120" s="6" t="s">
         <v>39</v>
-      </c>
-      <c r="C119" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="D119" s="6">
-        <v>30</v>
-      </c>
-      <c r="E119" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="F119" s="11" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A120" s="6">
-        <v>3</v>
-      </c>
-      <c r="B120" s="6" t="s">
-        <v>40</v>
       </c>
       <c r="C120" s="6" t="s">
         <v>61</v>
@@ -2747,15 +2760,15 @@
         <v>64</v>
       </c>
       <c r="F120" s="11" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.35">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B121" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C121" s="6" t="s">
         <v>61</v>
@@ -2763,162 +2776,164 @@
       <c r="D121" s="6">
         <v>30</v>
       </c>
-      <c r="E121" s="7"/>
+      <c r="E121" s="7" t="s">
+        <v>64</v>
+      </c>
       <c r="F121" s="11" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A122" s="6">
+        <v>4</v>
+      </c>
+      <c r="B122" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C122" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D122" s="6">
+        <v>30</v>
+      </c>
+      <c r="E122" s="7"/>
+      <c r="F122" s="11" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A122" s="6">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A123" s="6">
         <v>5</v>
       </c>
-      <c r="B122" s="6" t="s">
+      <c r="B123" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="C122" s="6" t="s">
+      <c r="C123" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="D122" s="6"/>
-      <c r="E122" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="F122" s="11" t="s">
+      <c r="D123" s="6"/>
+      <c r="E123" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="F123" s="11" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A123" s="6">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A124" s="6">
         <v>6</v>
       </c>
-      <c r="B123" s="6" t="s">
+      <c r="B124" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="C123" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="D123" s="6"/>
-      <c r="E123" s="7"/>
-      <c r="F123" s="11" t="s">
+      <c r="C124" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D124" s="6"/>
+      <c r="E124" s="7"/>
+      <c r="F124" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="G123" s="2">
+      <c r="G124" s="2">
         <v>15</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A125" s="10" t="s">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A126" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="B125" s="1" t="s">
+      <c r="B126" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A126" s="10" t="s">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A127" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="B126" s="1" t="s">
+      <c r="B127" s="1" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A127" s="4" t="s">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A128" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B127" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C127" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D127" s="4" t="s">
+      <c r="B128" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C128" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D128" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E127" s="5" t="s">
+      <c r="E128" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F127" s="5" t="s">
+      <c r="F128" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="128" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A128" s="6">
-        <v>1</v>
-      </c>
-      <c r="B128" s="6" t="s">
+    <row r="129" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A129" s="6">
+        <v>1</v>
+      </c>
+      <c r="B129" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C128" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="D128" s="6"/>
-      <c r="E128" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="F128" s="11" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A129" s="6">
-        <v>2</v>
-      </c>
-      <c r="B129" s="6" t="s">
-        <v>51</v>
-      </c>
       <c r="C129" s="6" t="s">
-        <v>101</v>
+        <v>59</v>
       </c>
       <c r="D129" s="6"/>
       <c r="E129" s="7" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="F129" s="11" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.35">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A130" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B130" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C130" s="6" t="s">
-        <v>60</v>
+        <v>101</v>
       </c>
       <c r="D130" s="6"/>
       <c r="E130" s="7" t="s">
         <v>64</v>
       </c>
       <c r="F130" s="11" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="131" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A131" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B131" s="6" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="C131" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D131" s="6"/>
       <c r="E131" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F131" s="11" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="132" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A132" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B132" s="6" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C132" s="6" t="s">
         <v>59</v>
@@ -2928,126 +2943,126 @@
         <v>63</v>
       </c>
       <c r="F132" s="11" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A133" s="6">
+        <v>5</v>
+      </c>
+      <c r="B133" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C133" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D133" s="6"/>
+      <c r="E133" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="F133" s="11" t="s">
         <v>187</v>
       </c>
-      <c r="G132" s="2">
+      <c r="G133" s="2">
         <v>16</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A134" s="10" t="s">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A135" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="B134" s="1" t="s">
+      <c r="B135" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A135" s="10" t="s">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A136" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="B135" s="1" t="s">
+      <c r="B136" s="1" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A136" s="4" t="s">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A137" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B136" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C136" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D136" s="4" t="s">
+      <c r="B137" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C137" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D137" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E136" s="5" t="s">
+      <c r="E137" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F136" s="5" t="s">
+      <c r="F137" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="137" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A137" s="6">
-        <v>1</v>
-      </c>
-      <c r="B137" s="6" t="s">
+    <row r="138" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A138" s="6">
+        <v>1</v>
+      </c>
+      <c r="B138" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C137" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="D137" s="6"/>
-      <c r="E137" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="F137" s="11" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A138" s="6">
-        <v>2</v>
-      </c>
-      <c r="B138" s="6" t="s">
-        <v>44</v>
-      </c>
       <c r="C138" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D138" s="6"/>
       <c r="E138" s="7" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="F138" s="11" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.35">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A139" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B139" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C139" s="6" t="s">
-        <v>101</v>
+        <v>60</v>
       </c>
       <c r="D139" s="6"/>
       <c r="E139" s="7" t="s">
         <v>64</v>
       </c>
       <c r="F139" s="11" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="140" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A140" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B140" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C140" s="6" t="s">
-        <v>59</v>
+        <v>101</v>
       </c>
       <c r="D140" s="6"/>
       <c r="E140" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F140" s="11" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="141" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A141" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B141" s="6" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="C141" s="6" t="s">
         <v>59</v>
@@ -3057,15 +3072,15 @@
         <v>63</v>
       </c>
       <c r="F141" s="11" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="142" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A142" s="6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B142" s="6" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="C142" s="6" t="s">
         <v>59</v>
@@ -3075,15 +3090,15 @@
         <v>63</v>
       </c>
       <c r="F142" s="11" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="143" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A143" s="6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B143" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C143" s="6" t="s">
         <v>59</v>
@@ -3093,15 +3108,15 @@
         <v>63</v>
       </c>
       <c r="F143" s="11" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="144" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A144" s="6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B144" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C144" s="6" t="s">
         <v>59</v>
@@ -3111,92 +3126,90 @@
         <v>63</v>
       </c>
       <c r="F144" s="11" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A145" s="6">
+        <v>8</v>
+      </c>
+      <c r="B145" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C145" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D145" s="6"/>
+      <c r="E145" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="F145" s="11" t="s">
         <v>195</v>
       </c>
-      <c r="G144" s="2">
+      <c r="G145" s="2">
         <v>17</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A146" s="10" t="s">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A147" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="B146" s="1" t="s">
+      <c r="B147" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A147" s="10" t="s">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A148" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="B147" s="1" t="s">
+      <c r="B148" s="1" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A148" s="4" t="s">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A149" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B148" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C148" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D148" s="4" t="s">
+      <c r="B149" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C149" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D149" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E148" s="5" t="s">
+      <c r="E149" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F148" s="5" t="s">
+      <c r="F149" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="149" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A149" s="6">
-        <v>1</v>
-      </c>
-      <c r="B149" s="6" t="s">
+    <row r="150" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A150" s="6">
+        <v>1</v>
+      </c>
+      <c r="B150" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C149" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="D149" s="6"/>
-      <c r="E149" s="7" t="s">
+      <c r="C150" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D150" s="6"/>
+      <c r="E150" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="F149" s="11" t="s">
+      <c r="F150" s="11" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A150" s="6">
-        <v>2</v>
-      </c>
-      <c r="B150" s="6" t="s">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A151" s="6">
+        <v>2</v>
+      </c>
+      <c r="B151" s="6" t="s">
         <v>53</v>
-      </c>
-      <c r="C150" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="D150" s="6">
-        <v>30</v>
-      </c>
-      <c r="E150" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="F150" s="11" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A151" s="6">
-        <v>3</v>
-      </c>
-      <c r="B151" s="6" t="s">
-        <v>54</v>
       </c>
       <c r="C151" s="6" t="s">
         <v>61</v>
@@ -3208,15 +3221,15 @@
         <v>64</v>
       </c>
       <c r="F151" s="11" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.35">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A152" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B152" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C152" s="6" t="s">
         <v>61</v>
@@ -3224,55 +3237,55 @@
       <c r="D152" s="6">
         <v>30</v>
       </c>
-      <c r="E152" s="7"/>
+      <c r="E152" s="7" t="s">
+        <v>64</v>
+      </c>
       <c r="F152" s="11" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A153" s="6">
+        <v>4</v>
+      </c>
+      <c r="B153" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C153" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D153" s="6">
+        <v>30</v>
+      </c>
+      <c r="E153" s="7"/>
+      <c r="F153" s="11" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="153" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A153" s="6">
+    <row r="154" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A154" s="6">
         <v>5</v>
       </c>
-      <c r="B153" s="6" t="s">
+      <c r="B154" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C153" s="6" t="s">
+      <c r="C154" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="D153" s="6"/>
-      <c r="E153" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="F153" s="11" t="s">
+      <c r="D154" s="6"/>
+      <c r="E154" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="F154" s="11" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A154" s="6">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A155" s="6">
         <v>6</v>
       </c>
-      <c r="B154" s="6" t="s">
+      <c r="B155" s="6" t="s">
         <v>56</v>
-      </c>
-      <c r="C154" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="D154" s="6">
-        <v>20</v>
-      </c>
-      <c r="E154" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="F154" s="11" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A155" s="6">
-        <v>7</v>
-      </c>
-      <c r="B155" s="6" t="s">
-        <v>57</v>
       </c>
       <c r="C155" s="6" t="s">
         <v>61</v>
@@ -3284,27 +3297,47 @@
         <v>64</v>
       </c>
       <c r="F155" s="11" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A156" s="6">
+        <v>7</v>
+      </c>
+      <c r="B156" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C156" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D156" s="6">
+        <v>20</v>
+      </c>
+      <c r="E156" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="F156" s="11" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="156" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A156" s="6">
+    <row r="157" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A157" s="6">
         <v>8</v>
       </c>
-      <c r="B156" s="6" t="s">
+      <c r="B157" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="C156" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="D156" s="6"/>
-      <c r="E156" s="7" t="s">
+      <c r="C157" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D157" s="6"/>
+      <c r="E157" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="F156" s="11" t="s">
+      <c r="F157" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="G156" s="2">
+      <c r="G157" s="2">
         <v>18</v>
       </c>
     </row>

--- a/documentacion/DD Proyecto.xlsx
+++ b/documentacion/DD Proyecto.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shavi\Downloads\visual\Proyecto\RBE\documentacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D90EE08-E5EB-494B-A85F-3FC8EE9526D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9D9AD0A-C2C2-4BAD-8876-6A4223429807}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DICCIONARIO DE DATOS" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'DICCIONARIO DE DATOS'!$A$1:$F$157</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'DICCIONARIO DE DATOS'!$A$1:$F$158</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="201">
   <si>
     <t>Número</t>
   </si>
@@ -120,9 +120,6 @@
   </si>
   <si>
     <t>destino</t>
-  </si>
-  <si>
-    <t>duracion</t>
   </si>
   <si>
     <t>ruta</t>
@@ -645,6 +642,9 @@
   </si>
   <si>
     <t>Es el coste de la ruta por ticket para luego calcular el costo del ticket, con valor por defecto de 250</t>
+  </si>
+  <si>
+    <t>Es costo por ticket base dentro de la ruta.</t>
   </si>
 </sst>
 </file>
@@ -1075,7 +1075,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A4:G157"/>
+  <dimension ref="A4:G158"/>
   <sheetFormatPr defaultColWidth="11.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.109375" style="2"/>
@@ -1089,18 +1089,18 @@
   <sheetData>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -1131,14 +1131,14 @@
         <v>21</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D7" s="6"/>
       <c r="E7" s="7" t="s">
         <v>7</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -1149,16 +1149,16 @@
         <v>8</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D8" s="6">
         <v>30</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -1166,18 +1166,18 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="B10" s="9" t="s">
         <v>66</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
@@ -1208,14 +1208,14 @@
         <v>13</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D13" s="6"/>
       <c r="E13" s="7" t="s">
         <v>7</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
@@ -1226,16 +1226,16 @@
         <v>14</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D14" s="6">
         <v>30</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
@@ -1246,16 +1246,16 @@
         <v>15</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D15" s="6">
         <v>30</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
@@ -1266,14 +1266,14 @@
         <v>16</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D16" s="6">
         <v>30</v>
       </c>
       <c r="E16" s="7"/>
       <c r="F16" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
@@ -1284,16 +1284,16 @@
         <v>17</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D17" s="6">
         <v>15</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1304,14 +1304,14 @@
         <v>18</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D18" s="6"/>
       <c r="E18" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1322,14 +1322,14 @@
         <v>19</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" s="6"/>
       <c r="E19" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G19" s="2">
         <v>2</v>
@@ -1337,18 +1337,18 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
@@ -1379,7 +1379,7 @@
         <v>20</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D24" s="6">
         <v>5</v>
@@ -1388,7 +1388,7 @@
         <v>7</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
@@ -1399,16 +1399,16 @@
         <v>8</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D25" s="6">
         <v>30</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G25" s="2">
         <v>3</v>
@@ -1416,18 +1416,18 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
@@ -1458,7 +1458,7 @@
         <v>21</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D30" s="6">
         <v>5</v>
@@ -1467,7 +1467,7 @@
         <v>7</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1478,16 +1478,16 @@
         <v>22</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D31" s="6">
         <v>30</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G31" s="2">
         <v>4</v>
@@ -1495,18 +1495,18 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
@@ -1537,14 +1537,14 @@
         <v>23</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D36" s="6"/>
       <c r="E36" s="7" t="s">
         <v>7</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
@@ -1555,14 +1555,14 @@
         <v>24</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D37" s="6"/>
       <c r="E37" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1573,16 +1573,16 @@
         <v>22</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D38" s="6">
         <v>30</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G38" s="2">
         <v>5</v>
@@ -1590,18 +1590,18 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
@@ -1632,14 +1632,14 @@
         <v>6</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D43" s="6"/>
       <c r="E43" s="7" t="s">
         <v>7</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
@@ -1650,16 +1650,16 @@
         <v>8</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D44" s="6">
         <v>30</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1670,16 +1670,16 @@
         <v>22</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D45" s="6">
         <v>50</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G45" s="2">
         <v>6</v>
@@ -1687,18 +1687,18 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B48" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
@@ -1729,14 +1729,14 @@
         <v>6</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D50" s="6"/>
       <c r="E50" s="7" t="s">
         <v>7</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
@@ -1747,16 +1747,16 @@
         <v>8</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D51" s="6">
         <v>30</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F51" s="11" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1767,14 +1767,14 @@
         <v>9</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D52" s="6"/>
       <c r="E52" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1785,14 +1785,14 @@
         <v>10</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D53" s="6"/>
       <c r="E53" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1803,14 +1803,14 @@
         <v>11</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D54" s="6"/>
       <c r="E54" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1821,14 +1821,14 @@
         <v>12</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D55" s="6"/>
       <c r="E55" s="7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F55" s="11" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G55" s="2">
         <v>7</v>
@@ -1836,18 +1836,18 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
@@ -1878,14 +1878,14 @@
         <v>6</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D60" s="6"/>
       <c r="E60" s="7" t="s">
         <v>7</v>
       </c>
       <c r="F60" s="11" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
@@ -1896,16 +1896,16 @@
         <v>8</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D61" s="6">
         <v>30</v>
       </c>
       <c r="E61" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F61" s="11" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1916,16 +1916,16 @@
         <v>22</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D62" s="6">
         <v>50</v>
       </c>
       <c r="E62" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G62" s="2">
         <v>8</v>
@@ -1933,18 +1933,18 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
@@ -1975,14 +1975,14 @@
         <v>6</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D67" s="6"/>
       <c r="E67" s="7" t="s">
         <v>7</v>
       </c>
       <c r="F67" s="11" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
@@ -1993,16 +1993,16 @@
         <v>8</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D68" s="6">
         <v>30</v>
       </c>
       <c r="E68" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F68" s="11" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
@@ -2010,19 +2010,19 @@
         <v>3</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D69" s="6">
         <v>30</v>
       </c>
       <c r="E69" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F69" s="11" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -2030,19 +2030,19 @@
         <v>4</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D70" s="6">
         <v>10</v>
       </c>
       <c r="E70" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F70" s="11" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="71" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -2050,19 +2050,19 @@
         <v>5</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D71" s="6">
         <v>29</v>
       </c>
       <c r="E71" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F71" s="11" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="72" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
@@ -2070,19 +2070,19 @@
         <v>6</v>
       </c>
       <c r="B72" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="C72" s="6" t="s">
         <v>197</v>
-      </c>
-      <c r="C72" s="6" t="s">
-        <v>198</v>
       </c>
       <c r="D72" s="6">
         <v>30</v>
       </c>
       <c r="E72" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="F72" s="11" t="s">
         <v>199</v>
-      </c>
-      <c r="F72" s="11" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="73" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
@@ -2093,16 +2093,16 @@
         <v>25</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D73" s="6">
         <v>5</v>
       </c>
       <c r="E73" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F73" s="11" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G73" s="2">
         <v>9</v>
@@ -2110,18 +2110,18 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
@@ -2152,52 +2152,52 @@
         <v>21</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D78" s="6"/>
       <c r="E78" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F78" s="11" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A79" s="6">
         <v>2</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>28</v>
+        <v>196</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="D79" s="6">
-        <v>10</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="D79" s="6"/>
       <c r="E79" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F79" s="11" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" s="6">
         <v>3</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="D80" s="6"/>
+        <v>60</v>
+      </c>
+      <c r="D80" s="6">
+        <v>10</v>
+      </c>
       <c r="E80" s="7" t="s">
         <v>63</v>
       </c>
       <c r="F80" s="11" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="81" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -2205,735 +2205,735 @@
         <v>4</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D81" s="6"/>
       <c r="E81" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F81" s="11" t="s">
-        <v>158</v>
-      </c>
-      <c r="G81" s="2">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A82" s="6">
+        <v>5</v>
+      </c>
+      <c r="B82" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C82" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D82" s="6"/>
+      <c r="E82" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="F82" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="G82" s="2">
         <v>10</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A83" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" s="10" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A85" s="4" t="s">
+      <c r="A85" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A86" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B85" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C85" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D85" s="4" t="s">
+      <c r="B86" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D86" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E85" s="5" t="s">
+      <c r="E86" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F85" s="5" t="s">
+      <c r="F86" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="86" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A86" s="6">
-        <v>1</v>
-      </c>
-      <c r="B86" s="6" t="s">
+    <row r="87" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A87" s="6">
+        <v>1</v>
+      </c>
+      <c r="B87" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C86" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="D86" s="6"/>
-      <c r="E86" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="F86" s="11" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A87" s="6">
-        <v>2</v>
-      </c>
-      <c r="B87" s="6" t="s">
-        <v>125</v>
-      </c>
       <c r="C87" s="6" t="s">
-        <v>101</v>
+        <v>58</v>
       </c>
       <c r="D87" s="6"/>
       <c r="E87" s="7" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="F87" s="11" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D88" s="6"/>
       <c r="E88" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F88" s="11" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>29</v>
+        <v>125</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>59</v>
+        <v>100</v>
       </c>
       <c r="D89" s="6"/>
       <c r="E89" s="7" t="s">
         <v>63</v>
       </c>
       <c r="F89" s="11" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="90" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A90" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D90" s="6"/>
       <c r="E90" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F90" s="11" t="s">
-        <v>165</v>
-      </c>
-      <c r="G90" s="2">
-        <v>11</v>
+        <v>163</v>
       </c>
     </row>
     <row r="91" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A91" s="6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D91" s="6"/>
       <c r="E91" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F91" s="11" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="92" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A92" s="6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D92" s="6"/>
       <c r="E92" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F92" s="11" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A94" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="B94" s="1" t="s">
-        <v>74</v>
+        <v>165</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A93" s="6">
+        <v>7</v>
+      </c>
+      <c r="B93" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C93" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D93" s="6"/>
+      <c r="E93" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="F93" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="G93" s="2">
+        <v>11</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" s="10" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A96" s="4" t="s">
+      <c r="A96" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A97" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B96" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C96" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D96" s="4" t="s">
+      <c r="B97" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D97" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E96" s="5" t="s">
+      <c r="E97" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F96" s="5" t="s">
+      <c r="F97" s="5" t="s">
         <v>5</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A97" s="6">
-        <v>1</v>
-      </c>
-      <c r="B97" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C97" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="D97" s="6"/>
-      <c r="E97" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F97" s="11" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="98" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A98" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D98" s="6"/>
       <c r="E98" s="7" t="s">
-        <v>63</v>
+        <v>7</v>
       </c>
       <c r="F98" s="11" t="s">
-        <v>107</v>
+        <v>158</v>
       </c>
     </row>
     <row r="99" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A99" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="D99" s="6">
-        <v>10</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="D99" s="6"/>
       <c r="E99" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F99" s="11" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="100" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A100" s="6">
+        <v>3</v>
+      </c>
+      <c r="B100" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C100" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="D100" s="6">
+        <v>10</v>
+      </c>
+      <c r="E100" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="F100" s="11" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A101" s="6">
         <v>4</v>
       </c>
-      <c r="B100" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="C100" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="D100" s="6">
+      <c r="B101" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="C101" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="D101" s="6">
         <v>17</v>
       </c>
-      <c r="E100" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="F100" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="G100" s="2">
+      <c r="E101" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="F101" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="G101" s="2">
         <v>12</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A102" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="B102" s="1" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103" s="10" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>96</v>
+        <v>72</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A104" s="4" t="s">
+      <c r="A104" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A105" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B104" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C104" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D104" s="4" t="s">
+      <c r="B105" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C105" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D105" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E104" s="5" t="s">
+      <c r="E105" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F104" s="5" t="s">
+      <c r="F105" s="5" t="s">
         <v>5</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A105" s="6">
-        <v>1</v>
-      </c>
-      <c r="B105" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C105" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="D105" s="6"/>
-      <c r="E105" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="F105" s="11" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="106" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A106" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="C106" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="D106" s="6">
+        <v>6</v>
+      </c>
+      <c r="C106" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D106" s="6"/>
+      <c r="E106" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="F106" s="11" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A107" s="6">
+        <v>2</v>
+      </c>
+      <c r="B107" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C107" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="D107" s="6">
         <v>5</v>
       </c>
-      <c r="E106" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="F106" s="11" t="s">
+      <c r="E107" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="F107" s="11" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A108" s="6">
+        <v>3</v>
+      </c>
+      <c r="B108" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C108" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D108" s="6"/>
+      <c r="E108" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="F108" s="11" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="107" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A107" s="6">
-        <v>3</v>
-      </c>
-      <c r="B107" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C107" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="D107" s="6"/>
-      <c r="E107" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="F107" s="11" t="s">
-        <v>170</v>
-      </c>
-      <c r="G107" s="2">
+      <c r="G108" s="2">
         <v>13</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A109" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="B109" s="1" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110" s="10" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>171</v>
+        <v>118</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A111" s="4" t="s">
+      <c r="A111" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A112" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B111" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C111" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D111" s="4" t="s">
+      <c r="B112" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C112" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D112" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E111" s="5" t="s">
+      <c r="E112" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F111" s="5" t="s">
+      <c r="F112" s="5" t="s">
         <v>5</v>
-      </c>
-    </row>
-    <row r="112" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A112" s="6">
-        <v>1</v>
-      </c>
-      <c r="B112" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C112" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="D112" s="6"/>
-      <c r="E112" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F112" s="11" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="113" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A113" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="C113" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D113" s="6"/>
       <c r="E113" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F113" s="11" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A114" s="6">
+        <v>2</v>
+      </c>
+      <c r="B114" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="F113" s="11" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A114" s="6">
-        <v>3</v>
-      </c>
-      <c r="B114" s="6" t="s">
-        <v>37</v>
-      </c>
       <c r="C114" s="6" t="s">
-        <v>128</v>
+        <v>58</v>
       </c>
       <c r="D114" s="6"/>
       <c r="E114" s="7" t="s">
-        <v>64</v>
+        <v>33</v>
       </c>
       <c r="F114" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="G114" s="2">
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A115" s="6">
+        <v>3</v>
+      </c>
+      <c r="B115" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C115" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="D115" s="6"/>
+      <c r="E115" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="F115" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="G115" s="2">
         <v>14</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A116" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="B116" s="1" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A118" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A119" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B119" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C119" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D119" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E119" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F119" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A120" s="6">
+        <v>1</v>
+      </c>
+      <c r="B120" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C120" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D120" s="6"/>
+      <c r="E120" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="B117" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A118" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B118" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C118" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D118" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E118" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="F118" s="5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A119" s="6">
-        <v>1</v>
-      </c>
-      <c r="B119" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C119" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="D119" s="6"/>
-      <c r="E119" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="F119" s="11" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A120" s="6">
-        <v>2</v>
-      </c>
-      <c r="B120" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="C120" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="D120" s="6">
-        <v>30</v>
-      </c>
-      <c r="E120" s="7" t="s">
-        <v>64</v>
-      </c>
       <c r="F120" s="11" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B121" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C121" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D121" s="6">
         <v>30</v>
       </c>
       <c r="E121" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F121" s="11" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A122" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B122" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C122" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D122" s="6">
         <v>30</v>
       </c>
-      <c r="E122" s="7"/>
+      <c r="E122" s="7" t="s">
+        <v>63</v>
+      </c>
       <c r="F122" s="11" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A123" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B123" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C123" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="D123" s="6"/>
-      <c r="E123" s="7" t="s">
-        <v>64</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="D123" s="6">
+        <v>30</v>
+      </c>
+      <c r="E123" s="7"/>
       <c r="F123" s="11" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A124" s="6">
+        <v>5</v>
+      </c>
+      <c r="B124" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C124" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D124" s="6"/>
+      <c r="E124" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="F124" s="11" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A125" s="6">
         <v>6</v>
       </c>
-      <c r="B124" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C124" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="D124" s="6"/>
-      <c r="E124" s="7"/>
-      <c r="F124" s="11" t="s">
-        <v>145</v>
-      </c>
-      <c r="G124" s="2">
+      <c r="B125" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C125" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D125" s="6"/>
+      <c r="E125" s="7"/>
+      <c r="F125" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="G125" s="2">
         <v>15</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A126" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="B126" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127" s="10" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>99</v>
+        <v>69</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A128" s="4" t="s">
+      <c r="A128" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A129" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B128" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C128" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D128" s="4" t="s">
+      <c r="B129" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C129" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D129" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E128" s="5" t="s">
+      <c r="E129" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F128" s="5" t="s">
+      <c r="F129" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="129" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A129" s="6">
-        <v>1</v>
-      </c>
-      <c r="B129" s="6" t="s">
+    <row r="130" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A130" s="6">
+        <v>1</v>
+      </c>
+      <c r="B130" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C129" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="D129" s="6"/>
-      <c r="E129" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="F129" s="11" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A130" s="6">
-        <v>2</v>
-      </c>
-      <c r="B130" s="6" t="s">
-        <v>51</v>
-      </c>
       <c r="C130" s="6" t="s">
-        <v>101</v>
+        <v>58</v>
       </c>
       <c r="D130" s="6"/>
       <c r="E130" s="7" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="F130" s="11" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A131" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B131" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C131" s="6" t="s">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="D131" s="6"/>
       <c r="E131" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F131" s="11" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="132" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A132" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B132" s="6" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="C132" s="6" t="s">
         <v>59</v>
@@ -2943,97 +2943,97 @@
         <v>63</v>
       </c>
       <c r="F132" s="11" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="133" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A133" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B133" s="6" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="C133" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D133" s="6"/>
       <c r="E133" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F133" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="G133" s="2">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A134" s="6">
+        <v>5</v>
+      </c>
+      <c r="B134" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C134" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D134" s="6"/>
+      <c r="E134" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="F134" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="G134" s="2">
         <v>16</v>
-      </c>
-    </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A135" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="B135" s="1" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A136" s="10" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>98</v>
+        <v>70</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A137" s="4" t="s">
+      <c r="A137" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A138" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B137" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C137" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D137" s="4" t="s">
+      <c r="B138" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C138" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D138" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E137" s="5" t="s">
+      <c r="E138" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F137" s="5" t="s">
+      <c r="F138" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="138" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A138" s="6">
-        <v>1</v>
-      </c>
-      <c r="B138" s="6" t="s">
+    <row r="139" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A139" s="6">
+        <v>1</v>
+      </c>
+      <c r="B139" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C138" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="D138" s="6"/>
-      <c r="E138" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="F138" s="11" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A139" s="6">
-        <v>2</v>
-      </c>
-      <c r="B139" s="6" t="s">
-        <v>44</v>
-      </c>
       <c r="C139" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D139" s="6"/>
       <c r="E139" s="7" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="F139" s="11" t="s">
         <v>188</v>
@@ -3041,53 +3041,53 @@
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A140" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B140" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C140" s="6" t="s">
-        <v>101</v>
+        <v>59</v>
       </c>
       <c r="D140" s="6"/>
       <c r="E140" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F140" s="11" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="141" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A141" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B141" s="6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C141" s="6" t="s">
-        <v>59</v>
+        <v>100</v>
       </c>
       <c r="D141" s="6"/>
       <c r="E141" s="7" t="s">
         <v>63</v>
       </c>
       <c r="F141" s="11" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="142" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A142" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B142" s="6" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="C142" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D142" s="6"/>
       <c r="E142" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F142" s="11" t="s">
         <v>191</v>
@@ -3095,249 +3095,267 @@
     </row>
     <row r="143" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A143" s="6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B143" s="6" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="C143" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D143" s="6"/>
       <c r="E143" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F143" s="11" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="144" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A144" s="6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B144" s="6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C144" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D144" s="6"/>
       <c r="E144" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F144" s="11" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="145" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A145" s="6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B145" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C145" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D145" s="6"/>
       <c r="E145" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F145" s="11" t="s">
-        <v>195</v>
-      </c>
-      <c r="G145" s="2">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A146" s="6">
+        <v>8</v>
+      </c>
+      <c r="B146" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C146" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D146" s="6"/>
+      <c r="E146" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="F146" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="G146" s="2">
         <v>17</v>
-      </c>
-    </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A147" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="B147" s="1" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A148" s="10" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>100</v>
+        <v>68</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A149" s="4" t="s">
+      <c r="A149" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A150" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B149" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C149" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D149" s="4" t="s">
+      <c r="B150" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C150" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D150" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E149" s="5" t="s">
+      <c r="E150" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F149" s="5" t="s">
+      <c r="F150" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="150" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A150" s="6">
-        <v>1</v>
-      </c>
-      <c r="B150" s="6" t="s">
+    <row r="151" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A151" s="6">
+        <v>1</v>
+      </c>
+      <c r="B151" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C150" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="D150" s="6"/>
-      <c r="E150" s="7" t="s">
+      <c r="C151" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D151" s="6"/>
+      <c r="E151" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="F150" s="11" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A151" s="6">
-        <v>2</v>
-      </c>
-      <c r="B151" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="C151" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="D151" s="6">
-        <v>30</v>
-      </c>
-      <c r="E151" s="7" t="s">
-        <v>64</v>
-      </c>
       <c r="F151" s="11" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A152" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B152" s="6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C152" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D152" s="6">
         <v>30</v>
       </c>
       <c r="E152" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F152" s="11" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A153" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B153" s="6" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C153" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D153" s="6">
         <v>30</v>
       </c>
-      <c r="E153" s="7"/>
+      <c r="E153" s="7" t="s">
+        <v>63</v>
+      </c>
       <c r="F153" s="11" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="154" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A154" s="6">
+        <v>4</v>
+      </c>
+      <c r="B154" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C154" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="D154" s="6">
+        <v>30</v>
+      </c>
+      <c r="E154" s="7"/>
+      <c r="F154" s="11" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A155" s="6">
         <v>5</v>
       </c>
-      <c r="B154" s="6" t="s">
+      <c r="B155" s="6" t="s">
         <v>19</v>
-      </c>
-      <c r="C154" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="D154" s="6"/>
-      <c r="E154" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="F154" s="11" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A155" s="6">
-        <v>6</v>
-      </c>
-      <c r="B155" s="6" t="s">
-        <v>56</v>
       </c>
       <c r="C155" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="D155" s="6">
-        <v>20</v>
-      </c>
+      <c r="D155" s="6"/>
       <c r="E155" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F155" s="11" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A156" s="6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B156" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C156" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D156" s="6">
         <v>20</v>
       </c>
       <c r="E156" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F156" s="11" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A157" s="6">
+        <v>7</v>
+      </c>
+      <c r="B157" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C157" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="D157" s="6">
+        <v>20</v>
+      </c>
+      <c r="E157" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="F157" s="11" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A158" s="6">
+        <v>8</v>
+      </c>
+      <c r="B158" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C158" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D158" s="6"/>
+      <c r="E158" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="F158" s="11" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="157" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A157" s="6">
-        <v>8</v>
-      </c>
-      <c r="B157" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="C157" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="D157" s="6"/>
-      <c r="E157" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="F157" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="G157" s="2">
+      <c r="G158" s="2">
         <v>18</v>
       </c>
     </row>

--- a/documentacion/DD Proyecto.xlsx
+++ b/documentacion/DD Proyecto.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shavi\Downloads\visual\Proyecto\RBE\documentacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9D9AD0A-C2C2-4BAD-8876-6A4223429807}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFD153F3-9140-43CC-8B21-059DA08C66A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5772" yWindow="372" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DICCIONARIO DE DATOS" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="203">
   <si>
     <t>Número</t>
   </si>
@@ -645,6 +645,12 @@
   </si>
   <si>
     <t>Es costo por ticket base dentro de la ruta.</t>
+  </si>
+  <si>
+    <t>supervisor</t>
+  </si>
+  <si>
+    <t>Marca si es un supervisor dentro de su terminal</t>
   </si>
 </sst>
 </file>
@@ -735,7 +741,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -772,6 +778,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1075,7 +1090,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A4:G158"/>
+  <dimension ref="A4:R159"/>
   <sheetFormatPr defaultColWidth="11.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.109375" style="2"/>
@@ -1939,7 +1954,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A65" s="10" t="s">
         <v>82</v>
       </c>
@@ -1947,7 +1962,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A66" s="4" t="s">
         <v>0</v>
       </c>
@@ -1967,7 +1982,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A67" s="6">
         <v>1</v>
       </c>
@@ -1985,7 +2000,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A68" s="6">
         <v>2</v>
       </c>
@@ -2005,7 +2020,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A69" s="6">
         <v>3</v>
       </c>
@@ -2025,7 +2040,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="70" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A70" s="6">
         <v>4</v>
       </c>
@@ -2044,8 +2059,14 @@
       <c r="F70" s="11" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="71" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="M70" s="3"/>
+      <c r="N70" s="3"/>
+      <c r="O70" s="3"/>
+      <c r="P70" s="3"/>
+      <c r="Q70" s="3"/>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A71" s="6">
         <v>5</v>
       </c>
@@ -2064,8 +2085,14 @@
       <c r="F71" s="11" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="72" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="M71" s="13"/>
+      <c r="N71" s="13"/>
+      <c r="O71" s="3"/>
+      <c r="P71" s="3"/>
+      <c r="Q71" s="3"/>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A72" s="6">
         <v>6</v>
       </c>
@@ -2084,8 +2111,14 @@
       <c r="F72" s="11" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="73" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="M72" s="14"/>
+      <c r="N72" s="15"/>
+      <c r="O72" s="3"/>
+      <c r="P72" s="3"/>
+      <c r="Q72" s="3"/>
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A73" s="6">
         <v>7</v>
       </c>
@@ -2107,24 +2140,50 @@
       <c r="G73" s="2">
         <v>9</v>
       </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="M73" s="14"/>
+      <c r="N73" s="15"/>
+      <c r="O73" s="3"/>
+      <c r="P73" s="3"/>
+      <c r="Q73" s="3"/>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="M74" s="14"/>
+      <c r="N74" s="15"/>
+      <c r="O74" s="3"/>
+      <c r="P74" s="3"/>
+      <c r="Q74" s="3"/>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A75" s="10" t="s">
         <v>65</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="M75" s="14"/>
+      <c r="N75" s="15"/>
+      <c r="O75" s="3"/>
+      <c r="P75" s="3"/>
+      <c r="Q75" s="3"/>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A76" s="10" t="s">
         <v>82</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="M76" s="14"/>
+      <c r="N76" s="15"/>
+      <c r="O76" s="3"/>
+      <c r="P76" s="3"/>
+      <c r="Q76" s="3"/>
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A77" s="4" t="s">
         <v>0</v>
       </c>
@@ -2143,8 +2202,14 @@
       <c r="F77" s="5" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="78" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="M77" s="3"/>
+      <c r="N77" s="3"/>
+      <c r="O77" s="3"/>
+      <c r="P77" s="3"/>
+      <c r="Q77" s="3"/>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="78" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A78" s="6">
         <v>1</v>
       </c>
@@ -2161,8 +2226,14 @@
       <c r="F78" s="11" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="79" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="M78" s="3"/>
+      <c r="N78" s="3"/>
+      <c r="O78" s="3"/>
+      <c r="P78" s="3"/>
+      <c r="Q78" s="3"/>
+      <c r="R78" s="3"/>
+    </row>
+    <row r="79" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A79" s="6">
         <v>2</v>
       </c>
@@ -2179,8 +2250,14 @@
       <c r="F79" s="11" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="M79" s="13"/>
+      <c r="N79" s="13"/>
+      <c r="O79" s="13"/>
+      <c r="P79" s="13"/>
+      <c r="Q79" s="13"/>
+      <c r="R79" s="13"/>
+    </row>
+    <row r="80" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A80" s="6">
         <v>3</v>
       </c>
@@ -2199,8 +2276,14 @@
       <c r="F80" s="11" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="81" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="M80" s="12"/>
+      <c r="N80" s="15"/>
+      <c r="O80" s="12"/>
+      <c r="P80" s="12"/>
+      <c r="Q80" s="12"/>
+      <c r="R80" s="12"/>
+    </row>
+    <row r="81" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A81" s="6">
         <v>4</v>
       </c>
@@ -2217,8 +2300,14 @@
       <c r="F81" s="11" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="82" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="M81" s="12"/>
+      <c r="N81" s="15"/>
+      <c r="O81" s="12"/>
+      <c r="P81" s="12"/>
+      <c r="Q81" s="12"/>
+      <c r="R81" s="12"/>
+    </row>
+    <row r="82" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A82" s="6">
         <v>5</v>
       </c>
@@ -2238,16 +2327,36 @@
       <c r="G82" s="2">
         <v>10</v>
       </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="M82" s="12"/>
+      <c r="N82" s="15"/>
+      <c r="O82" s="12"/>
+      <c r="P82" s="12"/>
+      <c r="Q82" s="12"/>
+      <c r="R82" s="12"/>
+    </row>
+    <row r="83" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="M83" s="12"/>
+      <c r="N83" s="15"/>
+      <c r="O83" s="12"/>
+      <c r="P83" s="12"/>
+      <c r="Q83" s="12"/>
+      <c r="R83" s="12"/>
+    </row>
+    <row r="84" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A84" s="10" t="s">
         <v>65</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="M84" s="12"/>
+      <c r="N84" s="15"/>
+      <c r="O84" s="12"/>
+      <c r="P84" s="12"/>
+      <c r="Q84" s="12"/>
+      <c r="R84" s="12"/>
+    </row>
+    <row r="85" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A85" s="10" t="s">
         <v>82</v>
       </c>
@@ -2255,7 +2364,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A86" s="4" t="s">
         <v>0</v>
       </c>
@@ -2275,7 +2384,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="87" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A87" s="6">
         <v>1</v>
       </c>
@@ -2293,7 +2402,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A88" s="6">
         <v>2</v>
       </c>
@@ -2311,7 +2420,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A89" s="6">
         <v>3</v>
       </c>
@@ -2329,7 +2438,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="90" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A90" s="6">
         <v>4</v>
       </c>
@@ -2347,7 +2456,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="91" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A91" s="6">
         <v>5</v>
       </c>
@@ -2365,7 +2474,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="92" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A92" s="6">
         <v>6</v>
       </c>
@@ -2383,7 +2492,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="93" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A93" s="6">
         <v>7</v>
       </c>
@@ -2404,7 +2513,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A95" s="10" t="s">
         <v>65</v>
       </c>
@@ -2412,7 +2521,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A96" s="10" t="s">
         <v>82</v>
       </c>
@@ -3357,6 +3466,22 @@
       </c>
       <c r="G158" s="2">
         <v>18</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A159" s="6">
+        <v>9</v>
+      </c>
+      <c r="B159" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="C159" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="D159" s="6"/>
+      <c r="E159" s="7"/>
+      <c r="F159" s="11" t="s">
+        <v>202</v>
       </c>
     </row>
   </sheetData>

--- a/documentacion/DD Proyecto.xlsx
+++ b/documentacion/DD Proyecto.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shavi\Downloads\visual\Proyecto\RBE\documentacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFD153F3-9140-43CC-8B21-059DA08C66A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AEDF649-6340-43D0-8187-B8D579B5515C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5772" yWindow="372" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DICCIONARIO DE DATOS" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'DICCIONARIO DE DATOS'!$A$1:$F$158</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'DICCIONARIO DE DATOS'!$A$1:$F$159</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -3486,10 +3486,12 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup scale="92" orientation="portrait" r:id="rId1"/>
-  <rowBreaks count="2" manualBreakCount="2">
-    <brk id="42" max="16383" man="1"/>
-    <brk id="106" max="16383" man="1"/>
+  <pageSetup scale="87" orientation="portrait" r:id="rId1"/>
+  <rowBreaks count="4" manualBreakCount="4">
+    <brk id="38" max="5" man="1"/>
+    <brk id="73" max="5" man="1"/>
+    <brk id="101" max="5" man="1"/>
+    <brk id="134" max="5" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
--- a/documentacion/DD Proyecto.xlsx
+++ b/documentacion/DD Proyecto.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shavi\Downloads\visual\Proyecto\RBE\documentacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{005CF209-9DC3-4A46-9C66-A3C5FBF31484}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C695BC3-70F9-438A-B3E6-289633C67D70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/documentacion/DD Proyecto.xlsx
+++ b/documentacion/DD Proyecto.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shavi\Downloads\visual\Proyecto\RBE\documentacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C695BC3-70F9-438A-B3E6-289633C67D70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5E1AA36-1E3B-4459-97C6-136FBA765F98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,8 @@
     <sheet name="DICCIONARIO DE DATOS" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'DICCIONARIO DE DATOS'!$A$1:$F$161</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'DICCIONARIO DE DATOS'!$A$1:$F$163</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'DICCIONARIO DE DATOS'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="209">
   <si>
     <t>Número</t>
   </si>
@@ -666,6 +667,9 @@
   </si>
   <si>
     <t>Gestionar la venta de boletos y manejo de rutas dentro de las terminales de autobuses</t>
+  </si>
+  <si>
+    <t>Es el precio base para calcular el coste del ticket</t>
   </si>
 </sst>
 </file>
@@ -764,7 +768,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -802,7 +806,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1108,7 +1111,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G163"/>
+  <dimension ref="A1:G164"/>
   <sheetFormatPr defaultColWidth="11.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.109375" style="2"/>
@@ -1120,7 +1123,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
         <v>205</v>
       </c>
       <c r="B1" s="1"/>
@@ -1155,7 +1158,7 @@
       <c r="A6" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" t="s">
         <v>116</v>
       </c>
       <c r="F6" s="12"/>
@@ -1783,7 +1786,7 @@
       <c r="A49" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="B49" s="13" t="s">
+      <c r="B49" t="s">
         <v>84</v>
       </c>
       <c r="F49" s="12"/>
@@ -2456,17 +2459,17 @@
         <v>4</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D92" s="6"/>
       <c r="E92" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F92" s="11" t="s">
-        <v>161</v>
+        <v>208</v>
       </c>
     </row>
     <row r="93" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -2474,7 +2477,7 @@
         <v>5</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C93" s="6" t="s">
         <v>58</v>
@@ -2484,7 +2487,7 @@
         <v>62</v>
       </c>
       <c r="F93" s="11" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="94" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -2492,7 +2495,7 @@
         <v>6</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C94" s="6" t="s">
         <v>58</v>
@@ -2502,7 +2505,7 @@
         <v>62</v>
       </c>
       <c r="F94" s="11" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="95" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -2510,7 +2513,7 @@
         <v>7</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C95" s="6" t="s">
         <v>58</v>
@@ -2520,297 +2523,297 @@
         <v>62</v>
       </c>
       <c r="F95" s="11" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A96" s="6">
+        <v>8</v>
+      </c>
+      <c r="B96" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C96" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D96" s="6"/>
+      <c r="E96" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="F96" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="G95" s="2">
+      <c r="G96" s="2">
         <v>11</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F96" s="12"/>
-    </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A97" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="B97" s="1" t="s">
-        <v>73</v>
-      </c>
       <c r="F97" s="12"/>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F98" s="12"/>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A99" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="B98" s="1" t="s">
+      <c r="B99" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="F98" s="12"/>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A99" s="4" t="s">
+      <c r="F99" s="12"/>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A100" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B99" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C99" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D99" s="4" t="s">
+      <c r="B100" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C100" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D100" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E99" s="5" t="s">
+      <c r="E100" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F99" s="5" t="s">
+      <c r="F100" s="5" t="s">
         <v>5</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A100" s="6">
-        <v>1</v>
-      </c>
-      <c r="B100" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C100" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="D100" s="6"/>
-      <c r="E100" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F100" s="11" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="101" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A101" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C101" s="6" t="s">
         <v>58</v>
       </c>
       <c r="D101" s="6"/>
       <c r="E101" s="7" t="s">
-        <v>62</v>
+        <v>7</v>
       </c>
       <c r="F101" s="11" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="102" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A102" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C102" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="D102" s="6">
-        <v>10</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="D102" s="6"/>
       <c r="E102" s="7" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F102" s="11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="103" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A103" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>112</v>
+        <v>31</v>
       </c>
       <c r="C103" s="6" t="s">
         <v>60</v>
       </c>
       <c r="D103" s="6">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E103" s="7" t="s">
         <v>64</v>
       </c>
       <c r="F103" s="11" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A104" s="6">
+        <v>4</v>
+      </c>
+      <c r="B104" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="C104" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="D104" s="6">
+        <v>17</v>
+      </c>
+      <c r="E104" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="F104" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="G103" s="2">
+      <c r="G104" s="2">
         <v>12</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F104" s="12"/>
-    </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A105" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="B105" s="1" t="s">
-        <v>72</v>
-      </c>
       <c r="F105" s="12"/>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F106" s="12"/>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A107" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="B106" s="1" t="s">
+      <c r="B107" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="F106" s="12"/>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A107" s="4" t="s">
+      <c r="F107" s="12"/>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A108" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B107" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C107" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D107" s="4" t="s">
+      <c r="B108" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C108" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D108" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E107" s="5" t="s">
+      <c r="E108" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F107" s="5" t="s">
+      <c r="F108" s="5" t="s">
         <v>5</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A108" s="6">
-        <v>1</v>
-      </c>
-      <c r="B108" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C108" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="D108" s="6"/>
-      <c r="E108" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="F108" s="11" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="109" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A109" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B109" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C109" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D109" s="6"/>
+      <c r="E109" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="F109" s="11" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A110" s="6">
+        <v>2</v>
+      </c>
+      <c r="B110" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C109" s="8" t="s">
+      <c r="C110" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D109" s="6">
+      <c r="D110" s="6">
         <v>5</v>
       </c>
-      <c r="E109" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="F109" s="11" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A110" s="6">
-        <v>3</v>
-      </c>
-      <c r="B110" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C110" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="D110" s="6"/>
       <c r="E110" s="7" t="s">
         <v>62</v>
       </c>
       <c r="F110" s="11" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A111" s="6">
+        <v>3</v>
+      </c>
+      <c r="B111" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C111" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D111" s="6"/>
+      <c r="E111" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="F111" s="11" t="s">
         <v>151</v>
       </c>
-      <c r="G110" s="2">
+      <c r="G111" s="2">
         <v>13</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F111" s="12"/>
-    </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A112" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="B112" s="1" t="s">
-        <v>104</v>
-      </c>
       <c r="F112" s="12"/>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="F113" s="12"/>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A114" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="B113" s="1" t="s">
+      <c r="B114" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="F113" s="12"/>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A114" s="4" t="s">
+      <c r="F114" s="12"/>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A115" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B114" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C114" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D114" s="4" t="s">
+      <c r="B115" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C115" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D115" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E114" s="5" t="s">
+      <c r="E115" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F114" s="5" t="s">
+      <c r="F115" s="5" t="s">
         <v>5</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A115" s="6">
-        <v>1</v>
-      </c>
-      <c r="B115" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="C115" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="D115" s="6"/>
-      <c r="E115" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="F115" s="11" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="116" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A116" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="C116" s="6" t="s">
         <v>58</v>
@@ -2820,115 +2823,113 @@
         <v>33</v>
       </c>
       <c r="F116" s="11" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A117" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C117" s="6" t="s">
-        <v>113</v>
+        <v>58</v>
       </c>
       <c r="D117" s="6"/>
       <c r="E117" s="7" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="F117" s="11" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A118" s="6">
+        <v>3</v>
+      </c>
+      <c r="B118" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C118" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="D118" s="6"/>
+      <c r="E118" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="F118" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="G117" s="2">
+      <c r="G118" s="2">
         <v>14</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F118" s="12"/>
-    </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A119" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="B119" s="1" t="s">
-        <v>71</v>
-      </c>
       <c r="F119" s="12"/>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A120" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F120" s="12"/>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A121" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="B120" s="1" t="s">
+      <c r="B121" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="F120" s="12"/>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A121" s="4" t="s">
+      <c r="F121" s="12"/>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A122" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B121" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C121" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D121" s="4" t="s">
+      <c r="B122" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C122" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D122" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E121" s="5" t="s">
+      <c r="E122" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F121" s="5" t="s">
+      <c r="F122" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="122" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A122" s="6">
-        <v>1</v>
-      </c>
-      <c r="B122" s="6" t="s">
+    <row r="123" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A123" s="6">
+        <v>1</v>
+      </c>
+      <c r="B123" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C122" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="D122" s="6"/>
-      <c r="E122" s="7" t="s">
+      <c r="C123" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D123" s="6"/>
+      <c r="E123" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="F122" s="11" t="s">
+      <c r="F123" s="11" t="s">
         <v>147</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A123" s="6">
-        <v>2</v>
-      </c>
-      <c r="B123" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="C123" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="D123" s="6">
-        <v>30</v>
-      </c>
-      <c r="E123" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="F123" s="11" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A124" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B124" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C124" s="6" t="s">
         <v>60</v>
@@ -2940,15 +2941,15 @@
         <v>63</v>
       </c>
       <c r="F124" s="11" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A125" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B125" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C125" s="6" t="s">
         <v>60</v>
@@ -2956,169 +2957,171 @@
       <c r="D125" s="6">
         <v>30</v>
       </c>
-      <c r="E125" s="7"/>
+      <c r="E125" s="7" t="s">
+        <v>63</v>
+      </c>
       <c r="F125" s="11" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126" s="6">
+        <v>4</v>
+      </c>
+      <c r="B126" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C126" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="D126" s="6">
+        <v>30</v>
+      </c>
+      <c r="E126" s="7"/>
+      <c r="F126" s="11" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A127" s="6">
         <v>5</v>
       </c>
-      <c r="B126" s="6" t="s">
+      <c r="B127" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C126" s="6" t="s">
+      <c r="C127" s="6" t="s">
         <v>61</v>
-      </c>
-      <c r="D126" s="6"/>
-      <c r="E126" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="F126" s="11" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A127" s="6">
-        <v>6</v>
-      </c>
-      <c r="B127" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C127" s="6" t="s">
-        <v>58</v>
       </c>
       <c r="D127" s="6"/>
       <c r="E127" s="7" t="s">
         <v>63</v>
       </c>
       <c r="F127" s="11" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A128" s="6">
+        <v>6</v>
+      </c>
+      <c r="B128" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C128" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D128" s="6"/>
+      <c r="E128" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="F128" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="G127" s="2">
+      <c r="G128" s="2">
         <v>15</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F128" s="12"/>
-    </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A129" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="B129" s="1" t="s">
-        <v>69</v>
-      </c>
       <c r="F129" s="12"/>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A130" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F130" s="12"/>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A131" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="B130" s="1" t="s">
+      <c r="B131" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="F130" s="12"/>
-    </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A131" s="4" t="s">
+      <c r="F131" s="12"/>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A132" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B131" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C131" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D131" s="4" t="s">
+      <c r="B132" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C132" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D132" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E131" s="5" t="s">
+      <c r="E132" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F131" s="5" t="s">
+      <c r="F132" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="132" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A132" s="6">
-        <v>1</v>
-      </c>
-      <c r="B132" s="6" t="s">
+    <row r="133" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A133" s="6">
+        <v>1</v>
+      </c>
+      <c r="B133" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C132" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="D132" s="6"/>
-      <c r="E132" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="F132" s="11" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A133" s="6">
-        <v>2</v>
-      </c>
-      <c r="B133" s="6" t="s">
-        <v>50</v>
-      </c>
       <c r="C133" s="6" t="s">
-        <v>100</v>
+        <v>58</v>
       </c>
       <c r="D133" s="6"/>
       <c r="E133" s="7" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="F133" s="11" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="134" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A134" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B134" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C134" s="6" t="s">
-        <v>59</v>
+        <v>100</v>
       </c>
       <c r="D134" s="6"/>
       <c r="E134" s="7" t="s">
         <v>63</v>
       </c>
       <c r="F134" s="11" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="135" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A135" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B135" s="6" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="C135" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D135" s="6"/>
       <c r="E135" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F135" s="11" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="136" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A136" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B136" s="6" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="C136" s="6" t="s">
         <v>58</v>
@@ -3128,131 +3131,131 @@
         <v>62</v>
       </c>
       <c r="F136" s="11" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A137" s="6">
+        <v>5</v>
+      </c>
+      <c r="B137" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C137" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D137" s="6"/>
+      <c r="E137" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="F137" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="G136" s="2">
+      <c r="G137" s="2">
         <v>16</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F137" s="12"/>
-    </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A138" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="B138" s="1" t="s">
-        <v>70</v>
-      </c>
       <c r="F138" s="12"/>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A139" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F139" s="12"/>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A140" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="B139" s="1" t="s">
+      <c r="B140" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="F139" s="12"/>
-    </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A140" s="4" t="s">
+      <c r="F140" s="12"/>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A141" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B140" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C140" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D140" s="4" t="s">
+      <c r="B141" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C141" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D141" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E140" s="5" t="s">
+      <c r="E141" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F140" s="5" t="s">
+      <c r="F141" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="141" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A141" s="6">
-        <v>1</v>
-      </c>
-      <c r="B141" s="6" t="s">
+    <row r="142" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A142" s="6">
+        <v>1</v>
+      </c>
+      <c r="B142" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C141" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="D141" s="6"/>
-      <c r="E141" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="F141" s="11" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="142" spans="1:7" ht="72" x14ac:dyDescent="0.3">
-      <c r="A142" s="6">
-        <v>2</v>
-      </c>
-      <c r="B142" s="6" t="s">
-        <v>43</v>
-      </c>
       <c r="C142" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D142" s="6"/>
       <c r="E142" s="7" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="F142" s="11" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A143" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B143" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C143" s="6" t="s">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="D143" s="6"/>
       <c r="E143" s="7" t="s">
         <v>63</v>
       </c>
       <c r="F143" s="11" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="144" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A144" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B144" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C144" s="6" t="s">
-        <v>58</v>
+        <v>100</v>
       </c>
       <c r="D144" s="6"/>
       <c r="E144" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F144" s="11" t="s">
-        <v>140</v>
+        <v>115</v>
       </c>
     </row>
     <row r="145" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A145" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B145" s="6" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="C145" s="6" t="s">
         <v>58</v>
@@ -3262,15 +3265,15 @@
         <v>62</v>
       </c>
       <c r="F145" s="11" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="146" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A146" s="6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B146" s="6" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="C146" s="6" t="s">
         <v>58</v>
@@ -3280,15 +3283,15 @@
         <v>62</v>
       </c>
       <c r="F146" s="11" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="147" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A147" s="6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B147" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C147" s="6" t="s">
         <v>58</v>
@@ -3298,15 +3301,15 @@
         <v>62</v>
       </c>
       <c r="F147" s="11" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="148" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A148" s="6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B148" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C148" s="6" t="s">
         <v>58</v>
@@ -3316,97 +3319,95 @@
         <v>62</v>
       </c>
       <c r="F148" s="11" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A149" s="6">
+        <v>8</v>
+      </c>
+      <c r="B149" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C149" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D149" s="6"/>
+      <c r="E149" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="F149" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="G148" s="2">
+      <c r="G149" s="2">
         <v>17</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F149" s="12"/>
-    </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A150" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="B150" s="1" t="s">
-        <v>68</v>
-      </c>
       <c r="F150" s="12"/>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A151" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F151" s="12"/>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A152" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="B151" s="1" t="s">
+      <c r="B152" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="F151" s="12"/>
-    </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A152" s="4" t="s">
+      <c r="F152" s="12"/>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A153" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B152" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C152" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D152" s="4" t="s">
+      <c r="B153" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C153" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D153" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E152" s="5" t="s">
+      <c r="E153" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F152" s="5" t="s">
+      <c r="F153" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="153" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A153" s="6">
-        <v>1</v>
-      </c>
-      <c r="B153" s="6" t="s">
+    <row r="154" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A154" s="6">
+        <v>1</v>
+      </c>
+      <c r="B154" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C153" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="D153" s="6"/>
-      <c r="E153" s="7" t="s">
+      <c r="C154" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D154" s="6"/>
+      <c r="E154" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="F153" s="11" t="s">
+      <c r="F154" s="11" t="s">
         <v>135</v>
-      </c>
-    </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A154" s="6">
-        <v>2</v>
-      </c>
-      <c r="B154" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="C154" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="D154" s="6">
-        <v>30</v>
-      </c>
-      <c r="E154" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="F154" s="11" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A155" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B155" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C155" s="6" t="s">
         <v>60</v>
@@ -3418,15 +3419,15 @@
         <v>63</v>
       </c>
       <c r="F155" s="11" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A156" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B156" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C156" s="6" t="s">
         <v>60</v>
@@ -3434,55 +3435,55 @@
       <c r="D156" s="6">
         <v>30</v>
       </c>
-      <c r="E156" s="7"/>
+      <c r="E156" s="7" t="s">
+        <v>63</v>
+      </c>
       <c r="F156" s="11" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A157" s="6">
+        <v>4</v>
+      </c>
+      <c r="B157" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C157" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="D157" s="6">
+        <v>30</v>
+      </c>
+      <c r="E157" s="7"/>
+      <c r="F157" s="11" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="157" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A157" s="6">
+    <row r="158" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A158" s="6">
         <v>5</v>
       </c>
-      <c r="B157" s="6" t="s">
+      <c r="B158" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C157" s="6" t="s">
+      <c r="C158" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="D157" s="6"/>
-      <c r="E157" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="F157" s="11" t="s">
+      <c r="D158" s="6"/>
+      <c r="E158" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="F158" s="11" t="s">
         <v>131</v>
-      </c>
-    </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A158" s="6">
-        <v>6</v>
-      </c>
-      <c r="B158" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="C158" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="D158" s="6">
-        <v>20</v>
-      </c>
-      <c r="E158" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="F158" s="11" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A159" s="6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B159" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C159" s="6" t="s">
         <v>60</v>
@@ -3494,60 +3495,83 @@
         <v>63</v>
       </c>
       <c r="F159" s="11" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A160" s="6">
+        <v>7</v>
+      </c>
+      <c r="B160" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C160" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="D160" s="6">
+        <v>20</v>
+      </c>
+      <c r="E160" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="F160" s="11" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="160" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A160" s="6">
+    <row r="161" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A161" s="6">
         <v>8</v>
       </c>
-      <c r="B160" s="6" t="s">
+      <c r="B161" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C160" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="D160" s="6"/>
-      <c r="E160" s="7" t="s">
+      <c r="C161" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D161" s="6"/>
+      <c r="E161" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="F160" s="11" t="s">
+      <c r="F161" s="11" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="161" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A161" s="6">
+    <row r="162" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A162" s="6">
         <v>9</v>
       </c>
-      <c r="B161" s="6" t="s">
+      <c r="B162" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="C161" s="6" t="s">
+      <c r="C162" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="D161" s="6"/>
-      <c r="E161" s="7"/>
-      <c r="F161" s="11" t="s">
+      <c r="D162" s="6"/>
+      <c r="E162" s="7"/>
+      <c r="F162" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="G161" s="2">
+      <c r="G162" s="2">
         <v>18</v>
       </c>
-    </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F162" s="12"/>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F163" s="12"/>
     </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F164" s="12"/>
+    </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
   <pageSetup scale="87" orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>&amp;RPagina &amp;P</oddFooter>
+  </headerFooter>
   <rowBreaks count="4" manualBreakCount="4">
     <brk id="39" max="5" man="1"/>
     <brk id="74" max="5" man="1"/>
-    <brk id="103" max="5" man="1"/>
-    <brk id="136" max="5" man="1"/>
+    <brk id="104" max="5" man="1"/>
+    <brk id="137" max="5" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>